--- a/009 SCS評価について/20260716_SCS評価_周期整理_v1.xlsx
+++ b/009 SCS評価について/20260716_SCS評価_周期整理_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KATOTO\Downloads\資料作成\shiryo\009 SCS評価について\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87871221-1218-43C6-9524-B3230AB4BD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F569653-7115-4D6C-9144-D9390CAE8D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="674">
   <si>
     <t>大分類No.</t>
   </si>
@@ -1606,11 +1606,6 @@
   </si>
   <si>
     <t>4-4-2-1</t>
-  </si>
-  <si>
-    <t>・利用するOS及びソフトウェアについて、以下のいずれかを適用すること。
-- 全てのOS及びソフトウェアについてサポートのあるものを利用すること。
-- やむを得ずサポート切れのOS及びソフトウェアを利用する場合(例えば、代替システムを調達する必要があり、直ちに更改できない場合)は、更改計画を策定した上で、更改するまでの間、No.4-4-4-2で求める脆弱性悪用のリスクを低減する対策を実施すること。</t>
   </si>
   <si>
     <t>サポート切れOS更改計画</t>
@@ -1716,12 +1711,6 @@
     <t>4-4-4-3</t>
   </si>
   <si>
-    <t>・インターネットとの境界に設置されているネットワーク機器のOS及びファームウェアについては、CVSS 基本値 7.0以上の脆弱性を有していないこと。</t>
-  </si>
-  <si>
-    <t>ネットワーク機器の脆弱性有無確認（CVSS7.0以上）</t>
-  </si>
-  <si>
     <t>4-4-5</t>
   </si>
   <si>
@@ -1738,9 +1727,6 @@
 </t>
   </si>
   <si>
-    <t>マルウェア対策ソフト導入</t>
-  </si>
-  <si>
     <t>4-4-5-2</t>
   </si>
   <si>
@@ -1909,9 +1895,6 @@
   </si>
   <si>
     <t>・ネットワーク機器のログ及びアラートを分析し、セキュリティ担当部署の担当者又は管理者により不審な事象が発見された場合に、それがセキュリティインシデントに該当するかが判断されること。</t>
-  </si>
-  <si>
-    <t>ログ・アラート分析体制</t>
   </si>
   <si>
     <t>5-1-1-3</t>
@@ -2245,12 +2228,223 @@
     <t>（新）セキュリティ対応方針か、KS-1037機密情報管理規定か</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>キッティングの際のマニュアル等？</t>
+    <rPh sb="7" eb="8">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>・利用するOS及びソフトウェアについて、以下のいずれかを適用すること。
+- 全てのOS及びソフトウェアについてサポートのあるものを利用すること。
+- やむを得ずサポート切れのOS及びソフトウェアを利用する場合(例えば、代替システムを調達する必要があり、直ちに更改できない場合)は、更改計画を策定した上で、更改するまでの間、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>No.4-4-4-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>で求める脆弱性悪用のリスクを低減する対策を実施すること。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アップデートのコントロールを家田さんがしているので、確認</t>
+    <rPh sb="14" eb="16">
+      <t>イエダ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネットワーク機器の脆弱性有無確認（CVSS7.0以上）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・インターネットとの境界に設置されているネットワーク機器のOS及びファームウェアについては、CVSS 基本値 7.0以上の脆弱性を有していないこと。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マルウェア対策ソフト導入</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネットワーク機器一覧確認・作成と、そのOSとファームウエアが確認できるWEBサイト</t>
+    <rPh sb="6" eb="8">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認（ネットワーク機器一覧）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認（該当ネットワーク機器一覧）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログ・アラート分析体制</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認（社外公開サーバー一覧）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シャガイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認（社内外ネットワークの境界と端末一覧）</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シャナイガイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョウカイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>タンマツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作る必要がある。</t>
+    <rPh sb="0" eb="1">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>作る必要がある。セキュリティ方針</t>
+    <rPh sb="0" eb="1">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報現状確認</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2299,6 +2493,14 @@
       <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="16">
@@ -3190,7 +3392,7 @@
         <v>14</v>
       </c>
       <c r="Q2" s="35" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
@@ -3607,7 +3809,7 @@
       <c r="N16" s="52"/>
       <c r="O16" s="50"/>
       <c r="P16" s="50" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="Q16" s="50"/>
     </row>
@@ -5962,7 +6164,7 @@
         <v>416</v>
       </c>
       <c r="Q100" s="50" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="101" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -5988,7 +6190,7 @@
         <v>419</v>
       </c>
       <c r="Q101" s="50" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="102" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -6016,7 +6218,7 @@
         <v>422</v>
       </c>
       <c r="Q102" s="50" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="103" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6056,7 +6258,7 @@
         <v>428</v>
       </c>
       <c r="Q103" s="50" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="104" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
@@ -6082,7 +6284,7 @@
         <v>431</v>
       </c>
       <c r="Q104" s="50" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="105" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
@@ -6110,7 +6312,7 @@
         <v>434</v>
       </c>
       <c r="Q105" s="50" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="106" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
@@ -6150,7 +6352,7 @@
         <v>442</v>
       </c>
       <c r="Q106" s="50" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="107" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
@@ -6176,7 +6378,7 @@
         <v>445</v>
       </c>
       <c r="Q107" s="50" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="108" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6212,7 +6414,7 @@
         <v>451</v>
       </c>
       <c r="Q108" s="50" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="109" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
@@ -6248,7 +6450,7 @@
         <v>457</v>
       </c>
       <c r="Q109" s="50" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="110" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -6286,7 +6488,7 @@
         <v>463</v>
       </c>
       <c r="Q110" s="50" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="111" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -6312,7 +6514,7 @@
         <v>466</v>
       </c>
       <c r="Q111" s="50" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="112" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -6499,7 +6701,9 @@
       <c r="P118" s="50" t="s">
         <v>492</v>
       </c>
-      <c r="Q118" s="50"/>
+      <c r="Q118" s="50" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="119" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B119" s="52"/>
@@ -6526,12 +6730,12 @@
         <v>496</v>
       </c>
       <c r="M119" s="46" t="s">
-        <v>497</v>
+        <v>659</v>
       </c>
       <c r="N119" s="52"/>
       <c r="O119" s="50"/>
       <c r="P119" s="50" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q119" s="50"/>
     </row>
@@ -6541,33 +6745,33 @@
       <c r="D120" s="52"/>
       <c r="E120" s="52"/>
       <c r="F120" s="57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G120" s="11"/>
       <c r="H120" s="59" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="51" t="s">
+        <v>499</v>
+      </c>
+      <c r="J120" s="51" t="s">
         <v>500</v>
-      </c>
-      <c r="J120" s="51" t="s">
-        <v>501</v>
       </c>
       <c r="K120" s="51" t="s">
         <v>6</v>
       </c>
       <c r="L120" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="M120" s="26" t="s">
         <v>502</v>
-      </c>
-      <c r="M120" s="26" t="s">
-        <v>503</v>
       </c>
       <c r="N120" s="52"/>
       <c r="O120" s="50" t="s">
+        <v>503</v>
+      </c>
+      <c r="P120" s="50" t="s">
         <v>504</v>
-      </c>
-      <c r="P120" s="50" t="s">
-        <v>505</v>
       </c>
       <c r="Q120" s="50"/>
     </row>
@@ -6583,15 +6787,15 @@
       <c r="J121" s="52"/>
       <c r="K121" s="52"/>
       <c r="L121" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="M121" s="26" t="s">
         <v>506</v>
-      </c>
-      <c r="M121" s="26" t="s">
-        <v>507</v>
       </c>
       <c r="N121" s="52"/>
       <c r="O121" s="50"/>
       <c r="P121" s="50" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q121" s="50"/>
     </row>
@@ -6607,17 +6811,17 @@
       <c r="J122" s="53"/>
       <c r="K122" s="53"/>
       <c r="L122" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="M122" s="26" t="s">
         <v>509</v>
-      </c>
-      <c r="M122" s="26" t="s">
-        <v>510</v>
       </c>
       <c r="N122" s="52"/>
       <c r="O122" s="50" t="s">
+        <v>510</v>
+      </c>
+      <c r="P122" s="50" t="s">
         <v>511</v>
-      </c>
-      <c r="P122" s="50" t="s">
-        <v>512</v>
       </c>
       <c r="Q122" s="50"/>
     </row>
@@ -6627,7 +6831,7 @@
       <c r="D123" s="52"/>
       <c r="E123" s="52"/>
       <c r="F123" s="57" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G123" s="55" t="s">
         <v>19</v>
@@ -6636,24 +6840,24 @@
         <v>19</v>
       </c>
       <c r="I123" s="51" t="s">
+        <v>513</v>
+      </c>
+      <c r="J123" s="51" t="s">
         <v>514</v>
-      </c>
-      <c r="J123" s="51" t="s">
-        <v>515</v>
       </c>
       <c r="K123" s="51" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="M123" s="26" t="s">
         <v>516</v>
-      </c>
-      <c r="M123" s="26" t="s">
-        <v>517</v>
       </c>
       <c r="N123" s="52"/>
       <c r="O123" s="50"/>
       <c r="P123" s="50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q123" s="50"/>
     </row>
@@ -6669,19 +6873,21 @@
       <c r="J124" s="52"/>
       <c r="K124" s="53"/>
       <c r="L124" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="M124" s="26" t="s">
         <v>519</v>
-      </c>
-      <c r="M124" s="26" t="s">
-        <v>520</v>
       </c>
       <c r="N124" s="52"/>
       <c r="O124" s="50" t="s">
+        <v>520</v>
+      </c>
+      <c r="P124" s="50" t="s">
         <v>521</v>
       </c>
-      <c r="P124" s="50" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q124" s="50"/>
+      <c r="Q124" s="50" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="125" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B125" s="52"/>
@@ -6697,17 +6903,19 @@
         <v>6</v>
       </c>
       <c r="L125" s="27" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M125" s="26" t="s">
-        <v>524</v>
+        <v>662</v>
       </c>
       <c r="N125" s="52"/>
       <c r="O125" s="50"/>
       <c r="P125" s="50" t="s">
-        <v>525</v>
-      </c>
-      <c r="Q125" s="50"/>
+        <v>661</v>
+      </c>
+      <c r="Q125" s="50" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="126" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B126" s="52"/>
@@ -6715,7 +6923,7 @@
       <c r="D126" s="52"/>
       <c r="E126" s="52"/>
       <c r="F126" s="74" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G126" s="55" t="s">
         <v>19</v>
@@ -6724,26 +6932,28 @@
         <v>19</v>
       </c>
       <c r="I126" s="51" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J126" s="51" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K126" s="51" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M126" s="26" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N126" s="52"/>
       <c r="O126" s="50"/>
       <c r="P126" s="50" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q126" s="50"/>
+        <v>663</v>
+      </c>
+      <c r="Q126" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="127" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B127" s="52"/>
@@ -6757,17 +6967,19 @@
       <c r="J127" s="52"/>
       <c r="K127" s="52"/>
       <c r="L127" s="22" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="M127" s="26" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="N127" s="52"/>
       <c r="O127" s="50"/>
       <c r="P127" s="50" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q127" s="50"/>
+        <v>530</v>
+      </c>
+      <c r="Q127" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="128" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B128" s="52"/>
@@ -6781,17 +6993,19 @@
       <c r="J128" s="52"/>
       <c r="K128" s="53"/>
       <c r="L128" s="22" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="M128" s="26" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="N128" s="52"/>
       <c r="O128" s="50"/>
       <c r="P128" s="50" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q128" s="50"/>
+        <v>533</v>
+      </c>
+      <c r="Q128" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="129" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B129" s="52"/>
@@ -6807,17 +7021,19 @@
         <v>6</v>
       </c>
       <c r="L129" s="27" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="M129" s="26" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="N129" s="52"/>
       <c r="O129" s="50"/>
       <c r="P129" s="50" t="s">
-        <v>540</v>
-      </c>
-      <c r="Q129" s="50"/>
+        <v>536</v>
+      </c>
+      <c r="Q129" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="130" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B130" s="52"/>
@@ -6831,29 +7047,31 @@
       <c r="J130" s="53"/>
       <c r="K130" s="53"/>
       <c r="L130" s="27" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="M130" s="26" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N130" s="52"/>
       <c r="O130" s="50"/>
       <c r="P130" s="50" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q130" s="50"/>
+        <v>539</v>
+      </c>
+      <c r="Q130" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="131" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B131" s="52"/>
       <c r="C131" s="52"/>
       <c r="D131" s="57" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E131" s="59" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F131" s="57" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G131" s="55" t="s">
         <v>19</v>
@@ -6862,26 +7080,28 @@
         <v>19</v>
       </c>
       <c r="I131" s="51" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J131" s="51" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K131" s="51" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="22" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="M131" s="26" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="N131" s="52"/>
       <c r="O131" s="50"/>
       <c r="P131" s="50" t="s">
-        <v>551</v>
-      </c>
-      <c r="Q131" s="50"/>
+        <v>547</v>
+      </c>
+      <c r="Q131" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="132" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="52"/>
@@ -6895,17 +7115,19 @@
       <c r="J132" s="52"/>
       <c r="K132" s="52"/>
       <c r="L132" s="22" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="M132" s="26" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="N132" s="52"/>
       <c r="O132" s="50"/>
       <c r="P132" s="50" t="s">
-        <v>554</v>
-      </c>
-      <c r="Q132" s="50"/>
+        <v>550</v>
+      </c>
+      <c r="Q132" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="133" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="52"/>
@@ -6919,17 +7141,19 @@
       <c r="J133" s="52"/>
       <c r="K133" s="52"/>
       <c r="L133" s="22" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="M133" s="26" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="N133" s="52"/>
       <c r="O133" s="50"/>
       <c r="P133" s="50" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q133" s="50"/>
+        <v>553</v>
+      </c>
+      <c r="Q133" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="134" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B134" s="52"/>
@@ -6943,17 +7167,19 @@
       <c r="J134" s="52"/>
       <c r="K134" s="52"/>
       <c r="L134" s="22" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M134" s="26" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="N134" s="52"/>
       <c r="O134" s="50"/>
       <c r="P134" s="50" t="s">
-        <v>560</v>
-      </c>
-      <c r="Q134" s="50"/>
+        <v>556</v>
+      </c>
+      <c r="Q134" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="135" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B135" s="52"/>
@@ -6967,17 +7193,19 @@
       <c r="J135" s="52"/>
       <c r="K135" s="52"/>
       <c r="L135" s="22" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="M135" s="26" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="N135" s="52"/>
       <c r="O135" s="50"/>
       <c r="P135" s="50" t="s">
-        <v>563</v>
-      </c>
-      <c r="Q135" s="50"/>
+        <v>559</v>
+      </c>
+      <c r="Q135" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="136" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B136" s="52"/>
@@ -6991,17 +7219,19 @@
       <c r="J136" s="52"/>
       <c r="K136" s="52"/>
       <c r="L136" s="22" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M136" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="N136" s="52"/>
       <c r="O136" s="50"/>
       <c r="P136" s="50" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q136" s="50"/>
+        <v>562</v>
+      </c>
+      <c r="Q136" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="137" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B137" s="52"/>
@@ -7015,17 +7245,19 @@
       <c r="J137" s="52"/>
       <c r="K137" s="53"/>
       <c r="L137" s="22" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M137" s="26" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="N137" s="52"/>
       <c r="O137" s="50"/>
       <c r="P137" s="50" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q137" s="50"/>
+        <v>565</v>
+      </c>
+      <c r="Q137" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="138" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B138" s="52"/>
@@ -7041,17 +7273,19 @@
         <v>6</v>
       </c>
       <c r="L138" s="22" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M138" s="26" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="N138" s="52"/>
       <c r="O138" s="50"/>
       <c r="P138" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="Q138" s="50"/>
+        <v>568</v>
+      </c>
+      <c r="Q138" s="50" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="139" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B139" s="53"/>
@@ -7065,33 +7299,35 @@
       <c r="J139" s="53"/>
       <c r="K139" s="53"/>
       <c r="L139" s="22" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="M139" s="26" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="N139" s="53"/>
       <c r="O139" s="50"/>
       <c r="P139" s="50" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q139" s="50"/>
+        <v>571</v>
+      </c>
+      <c r="Q139" s="50" t="s">
+        <v>669</v>
+      </c>
     </row>
     <row r="140" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B140" s="56">
         <v>5</v>
       </c>
       <c r="C140" s="56" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D140" s="54" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E140" s="56" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F140" s="54" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G140" s="56" t="s">
         <v>19</v>
@@ -7100,28 +7336,30 @@
         <v>19</v>
       </c>
       <c r="I140" s="51" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="J140" s="51" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="K140" s="51" t="s">
         <v>5</v>
       </c>
       <c r="L140" s="27" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M140" s="26" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N140" s="62" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="O140" s="50"/>
       <c r="P140" s="50" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q140" s="50"/>
+        <v>581</v>
+      </c>
+      <c r="Q140" s="50" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="141" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B141" s="52"/>
@@ -7135,17 +7373,19 @@
       <c r="J141" s="52"/>
       <c r="K141" s="52"/>
       <c r="L141" s="27" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="M141" s="26" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N141" s="52"/>
       <c r="O141" s="50"/>
       <c r="P141" s="50" t="s">
-        <v>588</v>
-      </c>
-      <c r="Q141" s="50"/>
+        <v>668</v>
+      </c>
+      <c r="Q141" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="142" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B142" s="52"/>
@@ -7159,17 +7399,19 @@
       <c r="J142" s="53"/>
       <c r="K142" s="53"/>
       <c r="L142" s="27" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="M142" s="26" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="N142" s="52"/>
       <c r="O142" s="50"/>
       <c r="P142" s="50" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q142" s="50"/>
+        <v>586</v>
+      </c>
+      <c r="Q142" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="143" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B143" s="52"/>
@@ -7177,33 +7419,35 @@
       <c r="D143" s="52"/>
       <c r="E143" s="52"/>
       <c r="F143" s="54" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G143" s="15"/>
       <c r="H143" s="56" t="s">
         <v>19</v>
       </c>
       <c r="I143" s="51" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="J143" s="51" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="K143" s="51" t="s">
         <v>6</v>
       </c>
       <c r="L143" s="22" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="M143" s="22" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="N143" s="52"/>
       <c r="O143" s="50"/>
       <c r="P143" s="50" t="s">
-        <v>597</v>
-      </c>
-      <c r="Q143" s="50"/>
+        <v>592</v>
+      </c>
+      <c r="Q143" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="144" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B144" s="52"/>
@@ -7217,17 +7461,17 @@
       <c r="J144" s="52"/>
       <c r="K144" s="52"/>
       <c r="L144" s="22" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="M144" s="26" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="N144" s="52"/>
       <c r="O144" s="50" t="s">
         <v>46</v>
       </c>
       <c r="P144" s="50" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="Q144" s="50"/>
     </row>
@@ -7243,55 +7487,59 @@
       <c r="J145" s="53"/>
       <c r="K145" s="53"/>
       <c r="L145" s="22" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="M145" s="26" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="N145" s="52"/>
       <c r="O145" s="50"/>
       <c r="P145" s="50" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q145" s="50"/>
+        <v>598</v>
+      </c>
+      <c r="Q145" s="50" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="146" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B146" s="52"/>
       <c r="C146" s="52"/>
       <c r="D146" s="54" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="E146" s="56" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="F146" s="54" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="G146" s="15"/>
       <c r="H146" s="56" t="s">
         <v>19</v>
       </c>
       <c r="I146" s="51" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="J146" s="51" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="K146" s="51" t="s">
         <v>6</v>
       </c>
       <c r="L146" s="22" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="M146" s="26" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="N146" s="52"/>
       <c r="O146" s="50"/>
       <c r="P146" s="50" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q146" s="50"/>
+        <v>606</v>
+      </c>
+      <c r="Q146" s="50" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="147" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B147" s="53"/>
@@ -7305,33 +7553,35 @@
       <c r="J147" s="53"/>
       <c r="K147" s="53"/>
       <c r="L147" s="22" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="M147" s="26" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="N147" s="53"/>
       <c r="O147" s="50"/>
       <c r="P147" s="50" t="s">
-        <v>614</v>
-      </c>
-      <c r="Q147" s="50"/>
+        <v>609</v>
+      </c>
+      <c r="Q147" s="50" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="148" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B148" s="61">
         <v>6</v>
       </c>
       <c r="C148" s="61" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D148" s="73" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="E148" s="61" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="F148" s="73" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="G148" s="67" t="s">
         <v>19</v>
@@ -7340,28 +7590,30 @@
         <v>19</v>
       </c>
       <c r="I148" s="70" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="J148" s="70" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="K148" s="70" t="s">
         <v>5</v>
       </c>
       <c r="L148" s="22" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="M148" s="26" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="N148" s="61" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="O148" s="50"/>
       <c r="P148" s="50" t="s">
-        <v>624</v>
-      </c>
-      <c r="Q148" s="50"/>
+        <v>619</v>
+      </c>
+      <c r="Q148" s="50" t="s">
+        <v>671</v>
+      </c>
     </row>
     <row r="149" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B149" s="52"/>
@@ -7375,17 +7627,19 @@
       <c r="J149" s="52"/>
       <c r="K149" s="52"/>
       <c r="L149" s="22" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="M149" s="26" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="N149" s="52"/>
       <c r="O149" s="50"/>
       <c r="P149" s="50" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q149" s="50"/>
+        <v>622</v>
+      </c>
+      <c r="Q149" s="50" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="150" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B150" s="52"/>
@@ -7399,10 +7653,10 @@
       <c r="J150" s="52"/>
       <c r="K150" s="52"/>
       <c r="L150" s="22" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="M150" s="26" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="N150" s="52"/>
       <c r="O150" s="50"/>
@@ -7423,17 +7677,17 @@
       <c r="J151" s="52"/>
       <c r="K151" s="52"/>
       <c r="L151" s="22" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="M151" s="26" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="N151" s="52"/>
       <c r="O151" s="50" t="s">
         <v>46</v>
       </c>
       <c r="P151" s="50" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="Q151" s="50"/>
     </row>
@@ -7449,15 +7703,15 @@
       <c r="J152" s="52"/>
       <c r="K152" s="52"/>
       <c r="L152" s="22" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="M152" s="26" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="N152" s="52"/>
       <c r="O152" s="50"/>
       <c r="P152" s="50" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="Q152" s="50"/>
     </row>
@@ -7473,17 +7727,17 @@
       <c r="J153" s="52"/>
       <c r="K153" s="52"/>
       <c r="L153" s="22" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="M153" s="26" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="N153" s="52"/>
       <c r="O153" s="50" t="s">
         <v>28</v>
       </c>
       <c r="P153" s="50" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="Q153" s="50"/>
     </row>
@@ -7492,16 +7746,16 @@
         <v>7</v>
       </c>
       <c r="C154" s="68" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="D154" s="71" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="E154" s="68" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="F154" s="71" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="G154" s="32" t="s">
         <v>19</v>
@@ -7510,26 +7764,26 @@
         <v>19</v>
       </c>
       <c r="I154" s="51" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="J154" s="51" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="K154" s="27" t="s">
         <v>5</v>
       </c>
       <c r="L154" s="22" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="M154" s="26" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="N154" s="68" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="O154" s="50"/>
       <c r="P154" s="50" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="Q154" s="50"/>
     </row>
@@ -7547,15 +7801,15 @@
         <v>6</v>
       </c>
       <c r="L155" s="22" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="M155" s="26" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="N155" s="53"/>
       <c r="O155" s="22"/>
       <c r="P155" s="50" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="Q155" s="50"/>
     </row>

--- a/009 SCS評価について/20260716_SCS評価_周期整理_v1.xlsx
+++ b/009 SCS評価について/20260716_SCS評価_周期整理_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KATOTO\Downloads\資料作成\shiryo\009 SCS評価について\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F569653-7115-4D6C-9144-D9390CAE8D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDFE21B-DAAF-4773-BC3D-A0835BE34693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,7 @@
     <definedName name="Z_DD069C75_829C_4DEA_B08C_DE5F18A8AF5A_.wvu.Rows" localSheetId="0" hidden="1">★3・★4要求事項・評価基準!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,8 +49,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="707">
   <si>
     <t>大分類No.</t>
   </si>
@@ -135,9 +134,6 @@
   </si>
   <si>
     <t>統治(GV)</t>
-  </si>
-  <si>
-    <t>社内ルール（関連法令・所管基準・取引先要求を踏まえて策定）</t>
   </si>
   <si>
     <t>1-1-1-2</t>
@@ -460,9 +456,6 @@
 - セキュリティ対策チェックシートを作成して回答を受領する</t>
   </si>
   <si>
-    <t>取引先セキュリティ対策状況の把握記録（チェックシート等）</t>
-  </si>
-  <si>
     <t>2-1-4</t>
   </si>
   <si>
@@ -571,9 +564,6 @@
     <t>・重要なシステムを構成する情報機器について、設定情報を把握するための仕組みを整備すること。</t>
   </si>
   <si>
-    <t>重要システム設定情報把握の仕組み</t>
-  </si>
-  <si>
     <t>3-1-1-7</t>
   </si>
   <si>
@@ -595,18 +585,12 @@
     <t>・ネットワークを把握するための仕組みを整備すること。その際、把握すべき情報の中に各ネットワークの所在地及び用途に関する情報を含めること。</t>
   </si>
   <si>
-    <t>ネットワーク把握の仕組み</t>
-  </si>
-  <si>
     <t>3-1-2-2</t>
   </si>
   <si>
     <t>・ネットワーク機器を把握するための仕組みを整備すること。その際、把握すべき情報の中に各機器の製造元、モデル及び保守事業者に関する情報を含めること。</t>
   </si>
   <si>
-    <t>ネットワーク機器把握の仕組み</t>
-  </si>
-  <si>
     <t>3-1-2-3</t>
   </si>
   <si>
@@ -638,9 +622,6 @@
   </si>
   <si>
     <t>外部情報サービスを利用する際のセキュリティ要件を定めたうえで、外部情報サービスの利用時に当該要件を満たしているかサービス内容を確認すること。</t>
-  </si>
-  <si>
-    <t>外部情報サービス利用のセキュリティ要件</t>
   </si>
   <si>
     <t>3-1-3-2</t>
@@ -835,9 +816,6 @@
     <t>・収集した脆弱性情報/脅威情報に対する対応履歴を記録し、対応漏れがないかどうかについて月次で点検すること。</t>
   </si>
   <si>
-    <t>月次</t>
-  </si>
-  <si>
     <t>対応履歴記録・点検記録</t>
   </si>
   <si>
@@ -888,9 +866,6 @@
     <t>・ユーザIDが不要になった場合(例えば、ユーザが組織を退職した場合又はユーザIDが一定期間使用されなかった場合)、速やかにユーザIDを削除又は無効化すること。</t>
   </si>
   <si>
-    <t>ユーザID削除・無効化手順</t>
-  </si>
-  <si>
     <t>4-1-1-4</t>
   </si>
   <si>
@@ -913,9 +888,6 @@
   </si>
   <si>
     <t>・すべてのサーバ及びネットワーク機器について、システム管理者及び責任者を定めること。</t>
-  </si>
-  <si>
-    <t>システム管理者・責任者の規定</t>
   </si>
   <si>
     <t>4-1-2-2</t>
@@ -926,9 +898,6 @@
 - やむを得ず管理者IDの共有が必要な場合(例えば、システムの仕様により、使用人数分のIDを発行することができない場合)は、共有の管理者IDを利用したユーザを特定できるようにすること。</t>
   </si>
   <si>
-    <t>管理者ID共有ルール（利用者特定含む）</t>
-  </si>
-  <si>
     <t>4-1-2-3</t>
   </si>
   <si>
@@ -953,9 +922,6 @@
     <t>・組織内でどの役員、従業員、派遣社員及び受入出向者が管理者IDを持っているかを把握するための仕組みを整備すること。</t>
   </si>
   <si>
-    <t>管理者ID保有状況把握の仕組み</t>
-  </si>
-  <si>
     <t>4-1-2-6</t>
   </si>
   <si>
@@ -1005,9 +971,6 @@
   </si>
   <si>
     <t>・重要な機密情報を取り扱うクラウドサービスにおいて、ユーザ及び管理者がサービスにアクセスする場合は、常にNo.4-1-3-3で示す認証要素を利用した多要素認証を使用すること。</t>
-  </si>
-  <si>
-    <t>多要素認証適用ルール（重要クラウドサービス）</t>
   </si>
   <si>
     <t>4-1-3-3</t>
@@ -2037,9 +2000,6 @@
   </si>
   <si>
     <t>・セキュリティインシデントの報告フォーマットを整備すること。</t>
-  </si>
-  <si>
-    <t>インシデント報告フォーマット</t>
   </si>
   <si>
     <t>6-1-1-6</t>
@@ -2439,12 +2399,559 @@
     <t>情報現状確認</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>規定を作る必要がある。</t>
+    <rPh sb="0" eb="2">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>インシデント報告フォーマット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サンプルから作成済</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルール化</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・事業継続上重要なシステム（情報のインフラストラクチャー規定）
+・業務の目標普旧レベルの決定
+・回復させる対策
+札幌へのバックアップのデータと、訓練が該当する</t>
+    <rPh sb="1" eb="3">
+      <t>ジギョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ケイゾクジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カイフク</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サッポロ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>クンレン</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ガイトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報システム部確認</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セキュリティに関する社内ルール（関連法令・所管基準・取引先要求を踏まえて策定）</t>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="4">
+      <t>シンキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>力量と体制</t>
+    <rPh sb="0" eb="2">
+      <t>リキリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定</t>
+    <rPh sb="7" eb="9">
+      <t>キミツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定から機密情報一覧を作成。取扱者と守秘義務を締結</t>
+    <rPh sb="17" eb="21">
+      <t>キミツジョウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>トリアツカイシャ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>シュヒギム</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テイケツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パロマ社内HPもしくは、ワークフローのタブのところに</t>
+    <rPh sb="3" eb="5">
+      <t>シャナイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メールで連絡（KS新規・改版連絡と同様に）</t>
+    <rPh sb="4" eb="6">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイハン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>点検記録</t>
+    <rPh sb="0" eb="2">
+      <t>テンケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一覧作成とそれを把握する仕組み作成</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハアク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定で網羅できるか？</t>
+    <rPh sb="16" eb="18">
+      <t>モウラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先セキュリティ対策状況の把握記録（チェックシート等）
+対象子会社・取引先一覧作成</t>
+    <rPh sb="29" eb="31">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>コガイシャ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>トリヒキサキ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SS1で可能</t>
+    <rPh sb="4" eb="6">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウカクニン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>体制・ルール　新規作成</t>
+    <rPh sb="0" eb="2">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シンキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>重要システム設定情報把握の仕組みと設定情報一覧
+重要なシステム一覧作成（情報システムインフラストラクチャー規定？）</t>
+    <rPh sb="17" eb="21">
+      <t>セッテイジョウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>キテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネットワーク把握の仕組み
+ネットワーク一覧</t>
+    <rPh sb="19" eb="21">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ネットワーク機器把握の仕組み
+ネットワーク機器一覧</t>
+    <rPh sb="21" eb="23">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外部情報サービス利用のセキュリティ要件
+外部情報サービス利用のセキュリティ要件確認書</t>
+    <rPh sb="39" eb="42">
+      <t>カクニンショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認、KS-2506　モバイルPC運用規定に含む？</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウカクニン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-2506　モバイルPC運用規定で周知</t>
+    <rPh sb="19" eb="21">
+      <t>シュウチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>月次</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取集ルールと体制と記録</t>
+    <rPh sb="0" eb="2">
+      <t>シュシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>脆弱性の確認方法</t>
+    <rPh sb="0" eb="3">
+      <t>ゼイジャクセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認（できていると思われる）</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウカクニン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認（対象は？OSのみか？データベース）</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウカクニン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認(フロー作成）</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンジョウカクニン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユーザID削除・無効化手順/業務フロー作成</t>
+    <rPh sb="14" eb="16">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>システム管理者・責任者の規定
+サーバーとネットワーク機器一覧</t>
+    <rPh sb="26" eb="28">
+      <t>キキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>管理者ID共有ルール（利用者特定含む）
+管理者ID管理一覧もしくは他で確認できるような資料</t>
+    <rPh sb="20" eb="23">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>管理者ID保有状況把握の仕組み
+一覧必要</t>
+    <rPh sb="16" eb="18">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>多要素認証適用ルール（重要クラウドサービス）
+クラウドサービス一覧</t>
+    <rPh sb="31" eb="33">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KSに新規作成？</t>
+    <rPh sb="3" eb="5">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>現状確認・KSに新規作成？</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KSの新規・改版通知で周知</t>
+    <rPh sb="3" eb="5">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイハン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュウチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定</t>
+  </si>
+  <si>
+    <t>KS-1037機密情報管理規定
+KS-1075 社内共有フォルダ管理規定</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報システム部部内標準⇒KS-1037機密情報管理規定</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ブナイヒョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成・ルール化</t>
+    <rPh sb="0" eb="4">
+      <t>シンキサクセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2501,6 +3008,23 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2764,7 +3288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2916,30 +3440,66 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2949,47 +3509,20 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
   <extLst>
@@ -3392,36 +3925,36 @@
         <v>14</v>
       </c>
       <c r="Q2" s="35" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="58">
+      <c r="B3" s="68">
         <v>1</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="68" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="60"/>
-      <c r="H3" s="58" t="s">
+      <c r="G3" s="59"/>
+      <c r="H3" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L3" s="22" t="s">
@@ -3430,632 +3963,676 @@
       <c r="M3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N3" s="68" t="s">
         <v>24</v>
       </c>
       <c r="O3" s="50"/>
-      <c r="P3" s="50" t="s">
+      <c r="P3" s="51" t="s">
+        <v>667</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="50"/>
-    </row>
-    <row r="4" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="22" t="s">
+      <c r="M4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="N4" s="57"/>
+      <c r="O4" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="O4" s="50" t="s">
+      <c r="P4" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="50" t="s">
+      <c r="Q4" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="50"/>
-    </row>
-    <row r="5" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="22" t="s">
+      <c r="M5" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="52"/>
+      <c r="N5" s="57"/>
       <c r="O5" s="50"/>
       <c r="P5" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="50"/>
-    </row>
-    <row r="6" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="64" t="s">
+      <c r="E6" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="F6" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="G6" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="51" t="s">
+      <c r="J6" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="51" t="s">
+      <c r="K6" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" s="27" t="s">
+      <c r="M6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="M6" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="52"/>
+      <c r="N6" s="57"/>
       <c r="O6" s="50"/>
       <c r="P6" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="50"/>
-    </row>
-    <row r="7" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="27" t="s">
+      <c r="M7" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="52"/>
+      <c r="N7" s="57"/>
       <c r="O7" s="50"/>
       <c r="P7" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q7" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="Q7" s="50"/>
-    </row>
-    <row r="8" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="27" t="s">
+      <c r="M8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="N8" s="57"/>
+      <c r="O8" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="52"/>
-      <c r="O8" s="50" t="s">
+      <c r="P8" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" s="50"/>
+      <c r="Q8" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="9" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="53"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="54"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="24" t="s">
         <v>6</v>
       </c>
       <c r="L9" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="52"/>
+      <c r="N9" s="57"/>
       <c r="O9" s="50"/>
       <c r="P9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="50"/>
-    </row>
-    <row r="10" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="64" t="s">
+      <c r="G10" s="4"/>
+      <c r="H10" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="51" t="s">
+      <c r="J10" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="51" t="s">
+      <c r="K10" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L10" s="22" t="s">
+      <c r="M10" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="52"/>
+      <c r="N10" s="57"/>
       <c r="O10" s="50"/>
       <c r="P10" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="50"/>
-    </row>
-    <row r="11" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="22" t="s">
+      <c r="M11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11" s="52"/>
+      <c r="N11" s="57"/>
       <c r="O11" s="50"/>
       <c r="P11" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q11" s="50" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="Q11" s="50"/>
-    </row>
-    <row r="12" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="64" t="s">
+      <c r="G12" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="51" t="s">
+      <c r="J12" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="51" t="s">
+      <c r="K12" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="M12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="M12" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="N12" s="52"/>
+      <c r="N12" s="57"/>
       <c r="O12" s="50"/>
       <c r="P12" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q12" s="50"/>
+        <v>60</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="13" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="53"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="54"/>
       <c r="L13" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="52"/>
+      <c r="N13" s="57"/>
       <c r="O13" s="50"/>
       <c r="P13" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="50" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="Q13" s="50"/>
-    </row>
-    <row r="14" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L14" s="22" t="s">
+      <c r="M14" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="N14" s="52"/>
+      <c r="N14" s="57"/>
       <c r="O14" s="50"/>
       <c r="P14" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q14" s="50" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="50"/>
-    </row>
-    <row r="15" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="22" t="s">
+      <c r="M15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" s="52"/>
+      <c r="N15" s="57"/>
       <c r="O15" s="50"/>
       <c r="P15" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="Q15" s="50"/>
-    </row>
-    <row r="16" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="64" t="s">
+      <c r="E16" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="F16" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="64" t="s">
+      <c r="G16" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="51" t="s">
+      <c r="J16" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="J16" s="51" t="s">
+      <c r="K16" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="22" t="s">
+      <c r="M16" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="M16" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="N16" s="52"/>
+      <c r="N16" s="57"/>
       <c r="O16" s="50"/>
       <c r="P16" s="50" t="s">
-        <v>653</v>
-      </c>
-      <c r="Q16" s="50"/>
+        <v>640</v>
+      </c>
+      <c r="Q16" s="50" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="17" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
       <c r="L17" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="M17" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="N17" s="52"/>
+      <c r="N17" s="57"/>
       <c r="O17" s="50"/>
       <c r="P17" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" s="50" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="Q17" s="50"/>
-    </row>
-    <row r="18" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="22" t="s">
+      <c r="M18" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="M18" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="N18" s="52"/>
+      <c r="N18" s="57"/>
       <c r="O18" s="50"/>
       <c r="P18" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q18" s="50"/>
+        <v>85</v>
+      </c>
+      <c r="Q18" s="50" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="19" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="42"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="24" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="M19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="M19" s="26" t="s">
+      <c r="N19" s="57"/>
+      <c r="O19" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="N19" s="52"/>
-      <c r="O19" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="P19" s="50" t="s">
+      <c r="Q19" s="50" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" ht="136.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="Q19" s="50"/>
-    </row>
-    <row r="20" spans="2:17" ht="136.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="64" t="s">
+      <c r="E20" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="F20" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="64" t="s">
+      <c r="G20" s="4"/>
+      <c r="H20" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="51" t="s">
+      <c r="J20" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="J20" s="51" t="s">
+      <c r="K20" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="K20" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L20" s="22" t="s">
+      <c r="M20" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="M20" s="26" t="s">
+      <c r="N20" s="57"/>
+      <c r="O20" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="N20" s="52"/>
-      <c r="O20" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="50" t="s">
+      <c r="Q20" s="50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="Q20" s="50"/>
-    </row>
-    <row r="21" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="22" t="s">
+      <c r="M21" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="M21" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N21" s="52"/>
+      <c r="N21" s="57"/>
       <c r="O21" s="50"/>
       <c r="P21" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q21" s="50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="68">
+        <v>2</v>
+      </c>
+      <c r="C22" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="Q21" s="50"/>
-    </row>
-    <row r="22" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="58">
-        <v>2</v>
-      </c>
-      <c r="C22" s="58" t="s">
+      <c r="D22" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="E22" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="F22" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="G22" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="51" t="s">
+      <c r="J22" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="J22" s="51" t="s">
+      <c r="K22" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="K22" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="27" t="s">
+      <c r="M22" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="M22" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="N22" s="52"/>
+      <c r="N22" s="57"/>
       <c r="O22" s="50"/>
       <c r="P22" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q22" s="50" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="Q22" s="50"/>
-    </row>
-    <row r="23" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="27" t="s">
+      <c r="M23" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="N23" s="57"/>
+      <c r="O23" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="N23" s="52"/>
-      <c r="O23" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P23" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q23" s="50"/>
+      <c r="Q23" s="50" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="24" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="54"/>
       <c r="G24" s="39"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="23" t="s">
         <v>6</v>
       </c>
       <c r="L24" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M24" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="M24" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="N24" s="52"/>
+      <c r="N24" s="57"/>
       <c r="O24" s="50"/>
       <c r="P24" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q24" s="50" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="40" t="s">
         <v>115</v>
-      </c>
-      <c r="Q24" s="50"/>
-    </row>
-    <row r="25" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="40" t="s">
-        <v>116</v>
       </c>
       <c r="G25" s="38" t="s">
         <v>19</v>
@@ -4064,70 +4641,74 @@
         <v>19</v>
       </c>
       <c r="I25" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="J25" s="22" t="s">
         <v>117</v>
-      </c>
-      <c r="J25" s="22" t="s">
-        <v>118</v>
       </c>
       <c r="K25" s="22" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="M25" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="N25" s="52"/>
+      <c r="N25" s="57"/>
       <c r="O25" s="50"/>
       <c r="P25" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q25" s="50" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" ht="214.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="40" t="s">
         <v>121</v>
-      </c>
-      <c r="Q25" s="50"/>
-    </row>
-    <row r="26" spans="2:17" ht="214.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="40" t="s">
-        <v>122</v>
       </c>
       <c r="G26" s="41"/>
       <c r="H26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" s="21" t="s">
         <v>123</v>
-      </c>
-      <c r="J26" s="21" t="s">
-        <v>124</v>
       </c>
       <c r="K26" s="22" t="s">
         <v>6</v>
       </c>
       <c r="L26" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="M26" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="N26" s="57"/>
+      <c r="O26" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P26" s="51" t="s">
+        <v>678</v>
+      </c>
+      <c r="Q26" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="40" t="s">
         <v>126</v>
-      </c>
-      <c r="N26" s="52"/>
-      <c r="O26" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P26" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q26" s="50"/>
-    </row>
-    <row r="27" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="G27" s="38" t="s">
         <v>19</v>
@@ -4136,3682 +4717,3860 @@
         <v>19</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K27" s="22" t="s">
         <v>5</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="N27" s="52"/>
+        <v>130</v>
+      </c>
+      <c r="N27" s="57"/>
       <c r="O27" s="50"/>
       <c r="P27" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q27" s="50"/>
+        <v>131</v>
+      </c>
+      <c r="Q27" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="28" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J28" s="21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K28" s="21" t="s">
         <v>6</v>
       </c>
       <c r="L28" s="22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="N28" s="53"/>
+        <v>136</v>
+      </c>
+      <c r="N28" s="54"/>
       <c r="O28" s="50"/>
       <c r="P28" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q28" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="61">
+        <v>3</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="Q28" s="50"/>
-    </row>
-    <row r="29" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="72">
-        <v>3</v>
-      </c>
-      <c r="C29" s="72" t="s">
+      <c r="E29" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="F29" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="72" t="s">
+      <c r="G29" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="F29" s="63" t="s">
+      <c r="J29" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="51" t="s">
+      <c r="K29" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="J29" s="51" t="s">
+      <c r="M29" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="K29" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="22" t="s">
+      <c r="N29" s="61" t="s">
         <v>146</v>
-      </c>
-      <c r="M29" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="N29" s="72" t="s">
-        <v>148</v>
       </c>
       <c r="O29" s="50"/>
       <c r="P29" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q29" s="50" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="M30" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="Q29" s="50"/>
-    </row>
-    <row r="30" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="M30" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="N30" s="52"/>
+      <c r="N30" s="57"/>
       <c r="O30" s="50"/>
       <c r="P30" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q30" s="50" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="M31" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="Q30" s="50"/>
-    </row>
-    <row r="31" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="M31" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="N31" s="52"/>
+      <c r="N31" s="57"/>
       <c r="O31" s="50"/>
       <c r="P31" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q31" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="M32" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="Q31" s="50"/>
-    </row>
-    <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="22" t="s">
+      <c r="N32" s="57"/>
+      <c r="O32" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P32" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="M32" s="44" t="s">
+      <c r="Q32" s="50" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L33" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="N32" s="52"/>
-      <c r="O32" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P32" s="50" t="s">
+      <c r="M33" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="Q32" s="50"/>
-    </row>
-    <row r="33" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L33" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="M33" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="N33" s="52"/>
+      <c r="N33" s="57"/>
       <c r="O33" s="50"/>
       <c r="P33" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q33" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" ht="48" x14ac:dyDescent="0.4">
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="M34" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="Q33" s="50"/>
-    </row>
-    <row r="34" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="22" t="s">
+      <c r="N34" s="57"/>
+      <c r="O34" s="50"/>
+      <c r="P34" s="51" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q34" s="50"/>
+    </row>
+    <row r="35" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="M34" s="21" t="s">
+      <c r="M35" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="N34" s="52"/>
-      <c r="O34" s="50"/>
-      <c r="P34" s="50" t="s">
+      <c r="N35" s="57"/>
+      <c r="O35" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P35" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q35" s="50"/>
+    </row>
+    <row r="36" spans="2:17" ht="48" x14ac:dyDescent="0.4">
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="Q34" s="50"/>
-    </row>
-    <row r="35" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="22" t="s">
+      <c r="G36" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="M35" s="44" t="s">
+      <c r="J36" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="N35" s="52"/>
-      <c r="O35" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P35" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q35" s="50"/>
-    </row>
-    <row r="36" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="63" t="s">
+      <c r="K36" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L36" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="G36" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" s="51" t="s">
+      <c r="M36" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="J36" s="51" t="s">
+      <c r="N36" s="57"/>
+      <c r="O36" s="50"/>
+      <c r="P36" s="51" t="s">
+        <v>683</v>
+      </c>
+      <c r="Q36" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" ht="48" x14ac:dyDescent="0.4">
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="K36" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L36" s="22" t="s">
+      <c r="M37" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="M36" s="26" t="s">
+      <c r="N37" s="57"/>
+      <c r="O37" s="50"/>
+      <c r="P37" s="51" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q37" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L38" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="N36" s="52"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50" t="s">
+      <c r="M38" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="Q36" s="50"/>
-    </row>
-    <row r="37" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="M37" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="N37" s="52"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q37" s="50"/>
-    </row>
-    <row r="38" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L38" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="M38" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="N38" s="52"/>
+      <c r="N38" s="57"/>
       <c r="O38" s="50"/>
       <c r="P38" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q38" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="M39" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="N39" s="57"/>
+      <c r="O39" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P39" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q39" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="G40" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="Q38" s="50"/>
-    </row>
-    <row r="39" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="27" t="s">
+      <c r="J40" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="M39" s="26" t="s">
+      <c r="K40" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L40" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="N39" s="52"/>
-      <c r="O39" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P39" s="50" t="s">
+      <c r="M40" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="Q39" s="50"/>
-    </row>
-    <row r="40" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="65" t="s">
+      <c r="N40" s="57"/>
+      <c r="O40" s="50"/>
+      <c r="P40" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q40" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="G40" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="51" t="s">
+      <c r="M41" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="J40" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L40" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="M40" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="N40" s="52"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q40" s="50"/>
-    </row>
-    <row r="41" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="M41" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="N41" s="52"/>
+      <c r="N41" s="57"/>
       <c r="O41" s="50"/>
       <c r="P41" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q41" s="50"/>
+        <v>184</v>
+      </c>
+      <c r="Q41" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="42" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="52"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="65" t="s">
-        <v>191</v>
-      </c>
-      <c r="G42" s="66" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="G42" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="72" t="s">
+      <c r="H42" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="J42" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="K42" s="51" t="s">
+      <c r="I42" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="J42" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="K42" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L42" s="22" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="N42" s="52"/>
+        <v>189</v>
+      </c>
+      <c r="N42" s="57"/>
       <c r="O42" s="50"/>
       <c r="P42" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q42" s="50"/>
+        <v>190</v>
+      </c>
+      <c r="Q42" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="43" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="52"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
       <c r="L43" s="22" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="N43" s="52"/>
+        <v>192</v>
+      </c>
+      <c r="N43" s="57"/>
       <c r="O43" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P43" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q43" s="50"/>
+        <v>193</v>
+      </c>
+      <c r="Q43" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="44" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="53"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="54"/>
       <c r="L44" s="22" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="N44" s="52"/>
+        <v>195</v>
+      </c>
+      <c r="N44" s="57"/>
       <c r="O44" s="50"/>
       <c r="P44" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q44" s="50"/>
+        <v>196</v>
+      </c>
+      <c r="Q44" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="45" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="51" t="s">
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L45" s="22" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M45" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="N45" s="52"/>
+        <v>198</v>
+      </c>
+      <c r="N45" s="57"/>
       <c r="O45" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P45" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q45" s="50"/>
+        <v>199</v>
+      </c>
+      <c r="Q45" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="46" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
       <c r="L46" s="22" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="M46" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="N46" s="52"/>
+        <v>201</v>
+      </c>
+      <c r="N46" s="57"/>
       <c r="O46" s="50"/>
       <c r="P46" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q46" s="50"/>
+        <v>202</v>
+      </c>
+      <c r="Q46" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="47" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
       <c r="G47" s="9"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
       <c r="L47" s="22" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="N47" s="52"/>
+        <v>204</v>
+      </c>
+      <c r="N47" s="57"/>
       <c r="O47" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P47" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q47" s="50"/>
+        <v>205</v>
+      </c>
+      <c r="Q47" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="48" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
       <c r="G48" s="9"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
       <c r="L48" s="22" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="N48" s="52"/>
+        <v>207</v>
+      </c>
+      <c r="N48" s="57"/>
       <c r="O48" s="50"/>
       <c r="P48" s="50" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q48" s="50"/>
+        <v>208</v>
+      </c>
+      <c r="Q48" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="49" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="53"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="54"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
       <c r="L49" s="22" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M49" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="N49" s="52"/>
+        <v>210</v>
+      </c>
+      <c r="N49" s="57"/>
       <c r="O49" s="50"/>
       <c r="P49" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q49" s="50"/>
+        <v>211</v>
+      </c>
+      <c r="Q49" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="50" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="63" t="s">
-        <v>218</v>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="62" t="s">
+        <v>212</v>
       </c>
       <c r="G50" s="3"/>
-      <c r="H50" s="72" t="s">
+      <c r="H50" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="I50" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="J50" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="K50" s="51" t="s">
+      <c r="I50" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="J50" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="K50" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L50" s="22" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M50" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="N50" s="52"/>
+        <v>216</v>
+      </c>
+      <c r="N50" s="57"/>
       <c r="O50" s="50"/>
       <c r="P50" s="50" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q50" s="50"/>
+        <v>217</v>
+      </c>
+      <c r="Q50" s="50" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="51" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="52"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
       <c r="G51" s="43"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
-      <c r="K51" s="52"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
       <c r="L51" s="22" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M51" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="N51" s="52"/>
+        <v>219</v>
+      </c>
+      <c r="N51" s="57"/>
       <c r="O51" s="50"/>
       <c r="P51" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q51" s="50" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="54"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="M52" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="N52" s="57"/>
+      <c r="O52" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="P52" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q52" s="50" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="E53" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="F53" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="Q51" s="50"/>
-    </row>
-    <row r="52" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
-      <c r="F52" s="53"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="53"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="K52" s="53"/>
-      <c r="L52" s="22" t="s">
+      <c r="G53" s="9"/>
+      <c r="H53" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="M52" s="26" t="s">
+      <c r="J53" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="N52" s="52"/>
-      <c r="O52" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="P52" s="50" t="s">
+      <c r="K53" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L53" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="Q52" s="50"/>
-    </row>
-    <row r="53" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="63" t="s">
+      <c r="M53" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E53" s="72" t="s">
-        <v>231</v>
-      </c>
-      <c r="F53" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="I53" s="51" t="s">
-        <v>233</v>
-      </c>
-      <c r="J53" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="K53" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L53" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="M53" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="N53" s="52"/>
+      <c r="N53" s="57"/>
       <c r="O53" s="50"/>
       <c r="P53" s="50" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q53" s="50"/>
+        <v>231</v>
+      </c>
+      <c r="Q53" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="54" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
       <c r="G54" s="9"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="52"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
+      <c r="K54" s="57"/>
       <c r="L54" s="22" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M54" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="N54" s="52"/>
+        <v>233</v>
+      </c>
+      <c r="N54" s="57"/>
       <c r="O54" s="50"/>
       <c r="P54" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q54" s="50"/>
+        <v>234</v>
+      </c>
+      <c r="Q54" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="55" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
       <c r="L55" s="22" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="N55" s="52"/>
+        <v>236</v>
+      </c>
+      <c r="N55" s="57"/>
       <c r="O55" s="50"/>
       <c r="P55" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q55" s="50"/>
+        <v>237</v>
+      </c>
+      <c r="Q55" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="56" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
-      <c r="K56" s="52"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="57"/>
       <c r="L56" s="22" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M56" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="N56" s="52"/>
+        <v>239</v>
+      </c>
+      <c r="N56" s="57"/>
       <c r="O56" s="50"/>
       <c r="P56" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q56" s="50" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="M57" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="N57" s="54"/>
+      <c r="O57" s="52" t="s">
+        <v>689</v>
+      </c>
+      <c r="P57" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q57" s="50" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B58" s="56">
+        <v>4</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="D58" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="E58" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="Q56" s="50"/>
-    </row>
-    <row r="57" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B57" s="53"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="53"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="53"/>
-      <c r="L57" s="22" t="s">
+      <c r="F58" s="63" t="s">
         <v>247</v>
       </c>
-      <c r="M57" s="26" t="s">
+      <c r="G58" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="N57" s="53"/>
-      <c r="O57" s="50" t="s">
+      <c r="J58" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="P57" s="50" t="s">
+      <c r="K58" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L58" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="Q57" s="50"/>
-    </row>
-    <row r="58" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="59">
-        <v>4</v>
-      </c>
-      <c r="C58" s="59" t="s">
+      <c r="M58" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="D58" s="57" t="s">
+      <c r="N58" s="56" t="s">
         <v>252</v>
-      </c>
-      <c r="E58" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="F58" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="G58" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I58" s="51" t="s">
-        <v>255</v>
-      </c>
-      <c r="J58" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="K58" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="M58" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="N58" s="59" t="s">
-        <v>259</v>
       </c>
       <c r="O58" s="50"/>
       <c r="P58" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q58" s="50"/>
+        <v>253</v>
+      </c>
+      <c r="Q58" s="50" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="59" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
       <c r="L59" s="22" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="M59" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="N59" s="52"/>
+        <v>255</v>
+      </c>
+      <c r="N59" s="57"/>
       <c r="O59" s="50"/>
       <c r="P59" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q59" s="50"/>
+        <v>256</v>
+      </c>
+      <c r="Q59" s="50" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="60" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
       <c r="L60" s="22" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="N60" s="52"/>
+        <v>258</v>
+      </c>
+      <c r="N60" s="57"/>
       <c r="O60" s="50"/>
       <c r="P60" s="50" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q60" s="50"/>
+        <v>695</v>
+      </c>
+      <c r="Q60" s="50" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="61" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
-      <c r="D61" s="52"/>
-      <c r="E61" s="52"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="53"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
       <c r="L61" s="22" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="M61" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="N61" s="52"/>
+        <v>260</v>
+      </c>
+      <c r="N61" s="57"/>
       <c r="O61" s="50"/>
       <c r="P61" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q61" s="50" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B62" s="57"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="J62" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="K62" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="M62" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="N62" s="57"/>
+      <c r="O62" s="50"/>
+      <c r="P62" s="51" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q62" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B63" s="57"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="57"/>
+      <c r="L63" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="M63" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="N63" s="57"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="51" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q63" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="Q61" s="50"/>
-    </row>
-    <row r="62" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="52"/>
-      <c r="C62" s="52"/>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="57" t="s">
+      <c r="M64" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="G62" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="J62" s="51" t="s">
-        <v>272</v>
-      </c>
-      <c r="K62" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="M62" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="N62" s="52"/>
-      <c r="O62" s="50"/>
-      <c r="P62" s="50" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q62" s="50"/>
-    </row>
-    <row r="63" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B63" s="52"/>
-      <c r="C63" s="52"/>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="52"/>
-      <c r="I63" s="52"/>
-      <c r="J63" s="52"/>
-      <c r="K63" s="52"/>
-      <c r="L63" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="M63" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="N63" s="52"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q63" s="50"/>
-    </row>
-    <row r="64" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
-      <c r="H64" s="52"/>
-      <c r="I64" s="52"/>
-      <c r="J64" s="52"/>
-      <c r="K64" s="52"/>
-      <c r="L64" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="M64" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="N64" s="52"/>
+      <c r="N64" s="57"/>
       <c r="O64" s="50"/>
       <c r="P64" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q64" s="50"/>
+        <v>271</v>
+      </c>
+      <c r="Q64" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="65" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B65" s="52"/>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="52"/>
-      <c r="K65" s="52"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
       <c r="L65" s="22" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="N65" s="52"/>
+        <v>273</v>
+      </c>
+      <c r="N65" s="57"/>
       <c r="O65" s="50"/>
       <c r="P65" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q65" s="50"/>
-    </row>
-    <row r="66" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="52"/>
-      <c r="J66" s="52"/>
-      <c r="K66" s="52"/>
+        <v>274</v>
+      </c>
+      <c r="Q65" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" ht="86.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
       <c r="L66" s="22" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="M66" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="N66" s="52"/>
+        <v>276</v>
+      </c>
+      <c r="N66" s="57"/>
       <c r="O66" s="50"/>
-      <c r="P66" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q66" s="50"/>
+      <c r="P66" s="51" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q66" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="67" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B67" s="52"/>
-      <c r="C67" s="52"/>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
-      <c r="H67" s="52"/>
-      <c r="I67" s="52"/>
-      <c r="J67" s="52"/>
-      <c r="K67" s="52"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="57"/>
       <c r="L67" s="22" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="M67" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="N67" s="52"/>
+        <v>278</v>
+      </c>
+      <c r="N67" s="57"/>
       <c r="O67" s="50"/>
       <c r="P67" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q67" s="50"/>
+        <v>279</v>
+      </c>
+      <c r="Q67" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="68" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="52"/>
-      <c r="C68" s="52"/>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
-      <c r="H68" s="52"/>
-      <c r="I68" s="52"/>
-      <c r="J68" s="52"/>
-      <c r="K68" s="52"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
       <c r="L68" s="22" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="M68" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="N68" s="52"/>
+        <v>281</v>
+      </c>
+      <c r="N68" s="57"/>
       <c r="O68" s="50"/>
       <c r="P68" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q68" s="50"/>
+        <v>282</v>
+      </c>
+      <c r="Q68" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="69" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B69" s="52"/>
-      <c r="C69" s="52"/>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="53"/>
-      <c r="I69" s="53"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="53"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
       <c r="L69" s="22" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="M69" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="N69" s="52"/>
+        <v>284</v>
+      </c>
+      <c r="N69" s="57"/>
       <c r="O69" s="50"/>
       <c r="P69" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q69" s="50"/>
+        <v>285</v>
+      </c>
+      <c r="Q69" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="70" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="52"/>
-      <c r="C70" s="52"/>
-      <c r="D70" s="52"/>
-      <c r="E70" s="52"/>
-      <c r="F70" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="G70" s="55" t="s">
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G70" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H70" s="59" t="s">
+      <c r="H70" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I70" s="51" t="s">
-        <v>298</v>
-      </c>
-      <c r="J70" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="K70" s="70" t="s">
+      <c r="I70" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="J70" s="55" t="s">
+        <v>288</v>
+      </c>
+      <c r="K70" s="72" t="s">
         <v>5</v>
       </c>
       <c r="L70" s="22" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="M70" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="N70" s="52"/>
+        <v>290</v>
+      </c>
+      <c r="N70" s="57"/>
       <c r="O70" s="50"/>
       <c r="P70" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q70" s="50"/>
-    </row>
-    <row r="71" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B71" s="52"/>
-      <c r="C71" s="52"/>
-      <c r="D71" s="52"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="52"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="52"/>
-      <c r="J71" s="52"/>
-      <c r="K71" s="52"/>
+        <v>291</v>
+      </c>
+      <c r="Q70" s="50" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" ht="99.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
       <c r="L71" s="22" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="M71" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="N71" s="52"/>
+        <v>293</v>
+      </c>
+      <c r="N71" s="57"/>
       <c r="O71" s="50"/>
-      <c r="P71" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q71" s="50"/>
+      <c r="P71" s="51" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q71" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="72" spans="2:17" ht="156" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="57"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
       <c r="L72" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="M72" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="N72" s="52"/>
+        <v>295</v>
+      </c>
+      <c r="N72" s="57"/>
       <c r="O72" s="50"/>
       <c r="P72" s="50" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q72" s="50"/>
+        <v>296</v>
+      </c>
+      <c r="Q72" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="73" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="52"/>
-      <c r="C73" s="52"/>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="52"/>
-      <c r="I73" s="52"/>
-      <c r="J73" s="52"/>
-      <c r="K73" s="52"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="57"/>
+      <c r="K73" s="57"/>
       <c r="L73" s="22" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="M73" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="N73" s="52"/>
+        <v>298</v>
+      </c>
+      <c r="N73" s="57"/>
       <c r="O73" s="50"/>
       <c r="P73" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q73" s="50"/>
+        <v>299</v>
+      </c>
+      <c r="Q73" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="74" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="53"/>
+      <c r="B74" s="57"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="54"/>
       <c r="G74" s="14"/>
-      <c r="H74" s="53"/>
-      <c r="I74" s="53"/>
-      <c r="J74" s="53"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
       <c r="K74" s="22" t="s">
         <v>6</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="M74" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="N74" s="52"/>
+        <v>301</v>
+      </c>
+      <c r="N74" s="57"/>
       <c r="O74" s="50"/>
       <c r="P74" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q74" s="50"/>
+        <v>302</v>
+      </c>
+      <c r="Q74" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="75" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="57" t="s">
-        <v>315</v>
-      </c>
-      <c r="G75" s="55" t="s">
+      <c r="B75" s="57"/>
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="63" t="s">
+        <v>303</v>
+      </c>
+      <c r="G75" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H75" s="55" t="s">
+      <c r="H75" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I75" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="J75" s="51" t="s">
-        <v>317</v>
-      </c>
-      <c r="K75" s="51" t="s">
+      <c r="I75" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="J75" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="K75" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L75" s="22" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="M75" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="N75" s="52"/>
+        <v>307</v>
+      </c>
+      <c r="N75" s="57"/>
       <c r="O75" s="50"/>
       <c r="P75" s="50" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q75" s="50"/>
+        <v>308</v>
+      </c>
+      <c r="Q75" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="76" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
-      <c r="J76" s="53"/>
-      <c r="K76" s="53"/>
+      <c r="B76" s="57"/>
+      <c r="C76" s="57"/>
+      <c r="D76" s="57"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="54"/>
+      <c r="J76" s="54"/>
+      <c r="K76" s="54"/>
       <c r="L76" s="22" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="M76" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="N76" s="52"/>
+        <v>310</v>
+      </c>
+      <c r="N76" s="57"/>
       <c r="O76" s="50"/>
       <c r="P76" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q76" s="50"/>
+        <v>311</v>
+      </c>
+      <c r="Q76" s="50" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="77" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B77" s="52"/>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="G77" s="55" t="s">
+      <c r="B77" s="57"/>
+      <c r="C77" s="57"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="G77" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H77" s="55" t="s">
+      <c r="H77" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I77" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="J77" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="K77" s="51" t="s">
+      <c r="I77" s="55" t="s">
+        <v>313</v>
+      </c>
+      <c r="J77" s="55" t="s">
+        <v>314</v>
+      </c>
+      <c r="K77" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L77" s="22" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="M77" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="N77" s="52"/>
+        <v>316</v>
+      </c>
+      <c r="N77" s="57"/>
       <c r="O77" s="50"/>
       <c r="P77" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q77" s="50"/>
+        <v>317</v>
+      </c>
+      <c r="Q77" s="50" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="78" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="52"/>
-      <c r="J78" s="52"/>
-      <c r="K78" s="52"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
+      <c r="J78" s="57"/>
+      <c r="K78" s="57"/>
       <c r="L78" s="22" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="N78" s="52"/>
+        <v>319</v>
+      </c>
+      <c r="N78" s="57"/>
       <c r="O78" s="50"/>
       <c r="P78" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q78" s="50"/>
+        <v>320</v>
+      </c>
+      <c r="Q78" s="50" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="79" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
-      <c r="J79" s="52"/>
-      <c r="K79" s="52"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="57"/>
       <c r="L79" s="22" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="M79" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="N79" s="52"/>
+        <v>322</v>
+      </c>
+      <c r="N79" s="57"/>
       <c r="O79" s="50"/>
       <c r="P79" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q79" s="50"/>
+        <v>323</v>
+      </c>
+      <c r="Q79" s="50" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="80" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
-      <c r="J80" s="52"/>
-      <c r="K80" s="52"/>
+      <c r="B80" s="57"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="57"/>
+      <c r="K80" s="57"/>
       <c r="L80" s="22" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="M80" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="N80" s="52"/>
+        <v>325</v>
+      </c>
+      <c r="N80" s="57"/>
       <c r="O80" s="50"/>
       <c r="P80" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q80" s="50"/>
+        <v>326</v>
+      </c>
+      <c r="Q80" s="50" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="81" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B81" s="52"/>
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="53"/>
-      <c r="I81" s="53"/>
-      <c r="J81" s="53"/>
-      <c r="K81" s="53"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="54"/>
+      <c r="I81" s="54"/>
+      <c r="J81" s="54"/>
+      <c r="K81" s="54"/>
       <c r="L81" s="22" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="M81" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="N81" s="52"/>
+        <v>328</v>
+      </c>
+      <c r="N81" s="57"/>
       <c r="O81" s="50"/>
       <c r="P81" s="50" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q81" s="50"/>
+        <v>329</v>
+      </c>
+      <c r="Q81" s="50" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="82" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B82" s="52"/>
-      <c r="C82" s="52"/>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="G82" s="55" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="G82" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H82" s="55" t="s">
+      <c r="H82" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I82" s="51" t="s">
-        <v>343</v>
-      </c>
-      <c r="J82" s="51" t="s">
-        <v>344</v>
-      </c>
-      <c r="K82" s="51" t="s">
+      <c r="I82" s="55" t="s">
+        <v>331</v>
+      </c>
+      <c r="J82" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="K82" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L82" s="22" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="M82" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="N82" s="52"/>
+        <v>334</v>
+      </c>
+      <c r="N82" s="57"/>
       <c r="O82" s="50"/>
       <c r="P82" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q82" s="50"/>
+        <v>335</v>
+      </c>
+      <c r="Q82" s="50" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="83" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B83" s="52"/>
-      <c r="C83" s="52"/>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="52"/>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="57"/>
+      <c r="H83" s="57"/>
+      <c r="I83" s="57"/>
+      <c r="J83" s="57"/>
+      <c r="K83" s="57"/>
       <c r="L83" s="22" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="M83" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="N83" s="52"/>
+        <v>337</v>
+      </c>
+      <c r="N83" s="57"/>
       <c r="O83" s="50"/>
       <c r="P83" s="50" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q83" s="50"/>
+        <v>338</v>
+      </c>
+      <c r="Q83" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="84" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="52"/>
-      <c r="C84" s="52"/>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="53"/>
-      <c r="G84" s="53"/>
-      <c r="H84" s="53"/>
-      <c r="I84" s="53"/>
-      <c r="J84" s="53"/>
-      <c r="K84" s="53"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54"/>
+      <c r="H84" s="54"/>
+      <c r="I84" s="54"/>
+      <c r="J84" s="54"/>
+      <c r="K84" s="54"/>
       <c r="L84" s="22" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>352</v>
-      </c>
-      <c r="N84" s="52"/>
+        <v>340</v>
+      </c>
+      <c r="N84" s="57"/>
       <c r="O84" s="50"/>
       <c r="P84" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q84" s="50"/>
+        <v>341</v>
+      </c>
+      <c r="Q84" s="50" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="85" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B85" s="52"/>
-      <c r="C85" s="52"/>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="57" t="s">
-        <v>354</v>
+      <c r="B85" s="57"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="63" t="s">
+        <v>342</v>
       </c>
       <c r="G85" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H85" s="59" t="s">
+      <c r="H85" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I85" s="51" t="s">
-        <v>355</v>
-      </c>
-      <c r="J85" s="51" t="s">
-        <v>356</v>
+      <c r="I85" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="J85" s="55" t="s">
+        <v>344</v>
       </c>
       <c r="K85" s="21" t="s">
         <v>5</v>
       </c>
       <c r="L85" s="22" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="M85" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="N85" s="52"/>
+        <v>346</v>
+      </c>
+      <c r="N85" s="57"/>
       <c r="O85" s="50"/>
       <c r="P85" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q85" s="50"/>
-    </row>
-    <row r="86" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
+        <v>347</v>
+      </c>
+      <c r="Q85" s="77" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17" ht="69" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
       <c r="G86" s="11"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="52"/>
-      <c r="K86" s="51" t="s">
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L86" s="27" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="M86" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="N86" s="52"/>
+        <v>349</v>
+      </c>
+      <c r="N86" s="57"/>
       <c r="O86" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P86" s="50" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q86" s="50"/>
+        <v>350</v>
+      </c>
+      <c r="Q86" s="77" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="87" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
       <c r="G87" s="12"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="57"/>
+      <c r="J87" s="57"/>
+      <c r="K87" s="57"/>
       <c r="L87" s="27" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="N87" s="52"/>
+        <v>352</v>
+      </c>
+      <c r="N87" s="57"/>
       <c r="O87" s="50"/>
       <c r="P87" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q87" s="50"/>
+        <v>353</v>
+      </c>
+      <c r="Q87" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="88" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
       <c r="G88" s="12"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
-      <c r="J88" s="52"/>
-      <c r="K88" s="52"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="57"/>
+      <c r="J88" s="57"/>
+      <c r="K88" s="57"/>
       <c r="L88" s="27" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="M88" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="N88" s="52"/>
+        <v>355</v>
+      </c>
+      <c r="N88" s="57"/>
       <c r="O88" s="50"/>
       <c r="P88" s="50" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q88" s="50"/>
+        <v>356</v>
+      </c>
+      <c r="Q88" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="89" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B89" s="52"/>
-      <c r="C89" s="52"/>
-      <c r="D89" s="52"/>
-      <c r="E89" s="52"/>
-      <c r="F89" s="52"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
       <c r="G89" s="12"/>
-      <c r="H89" s="52"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="57"/>
+      <c r="J89" s="57"/>
+      <c r="K89" s="57"/>
       <c r="L89" s="27" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="M89" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="N89" s="52"/>
+        <v>358</v>
+      </c>
+      <c r="N89" s="57"/>
       <c r="O89" s="50"/>
       <c r="P89" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q89" s="50"/>
+        <v>359</v>
+      </c>
+      <c r="Q89" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="90" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="52"/>
-      <c r="C90" s="52"/>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="53"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="54"/>
       <c r="G90" s="13"/>
-      <c r="H90" s="53"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
+      <c r="H90" s="54"/>
+      <c r="I90" s="54"/>
+      <c r="J90" s="54"/>
+      <c r="K90" s="54"/>
       <c r="L90" s="27" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="M90" s="26" t="s">
-        <v>373</v>
-      </c>
-      <c r="N90" s="52"/>
+        <v>361</v>
+      </c>
+      <c r="N90" s="57"/>
       <c r="O90" s="50"/>
       <c r="P90" s="50" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q90" s="50"/>
+        <v>362</v>
+      </c>
+      <c r="Q90" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="91" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B91" s="52"/>
-      <c r="C91" s="52"/>
-      <c r="D91" s="52"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="57" t="s">
-        <v>375</v>
+      <c r="B91" s="57"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="63" t="s">
+        <v>363</v>
       </c>
       <c r="G91" s="12"/>
-      <c r="H91" s="59" t="s">
+      <c r="H91" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I91" s="51" t="s">
-        <v>376</v>
-      </c>
-      <c r="J91" s="51" t="s">
-        <v>377</v>
-      </c>
-      <c r="K91" s="51" t="s">
+      <c r="I91" s="55" t="s">
+        <v>364</v>
+      </c>
+      <c r="J91" s="55" t="s">
+        <v>365</v>
+      </c>
+      <c r="K91" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L91" s="22" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="N91" s="52"/>
+        <v>367</v>
+      </c>
+      <c r="N91" s="57"/>
       <c r="O91" s="50"/>
       <c r="P91" s="50" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q91" s="50"/>
+        <v>368</v>
+      </c>
+      <c r="Q91" s="50" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="92" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="52"/>
-      <c r="C92" s="52"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="52"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
       <c r="G92" s="12"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="57"/>
       <c r="L92" s="22" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="M92" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="N92" s="52"/>
+        <v>370</v>
+      </c>
+      <c r="N92" s="57"/>
       <c r="O92" s="50"/>
       <c r="P92" s="50" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q92" s="50"/>
+        <v>371</v>
+      </c>
+      <c r="Q92" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="93" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B93" s="52"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
       <c r="G93" s="12"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
+      <c r="K93" s="57"/>
       <c r="L93" s="22" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>385</v>
-      </c>
-      <c r="N93" s="52"/>
+        <v>373</v>
+      </c>
+      <c r="N93" s="57"/>
       <c r="O93" s="50"/>
       <c r="P93" s="50" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q93" s="50"/>
+        <v>374</v>
+      </c>
+      <c r="Q93" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="94" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="52"/>
-      <c r="C94" s="52"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="53"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="54"/>
       <c r="G94" s="12"/>
-      <c r="H94" s="53"/>
-      <c r="I94" s="53"/>
-      <c r="J94" s="53"/>
-      <c r="K94" s="53"/>
+      <c r="H94" s="54"/>
+      <c r="I94" s="54"/>
+      <c r="J94" s="54"/>
+      <c r="K94" s="54"/>
       <c r="L94" s="22" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="N94" s="52"/>
+        <v>376</v>
+      </c>
+      <c r="N94" s="57"/>
       <c r="O94" s="50" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="P94" s="50" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q94" s="50"/>
+        <v>378</v>
+      </c>
+      <c r="Q94" s="50" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="95" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="57" t="s">
-        <v>391</v>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="63" t="s">
+        <v>379</v>
       </c>
       <c r="G95" s="30"/>
-      <c r="H95" s="59" t="s">
+      <c r="H95" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I95" s="51" t="s">
-        <v>392</v>
-      </c>
-      <c r="J95" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="K95" s="51" t="s">
+      <c r="I95" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="J95" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="K95" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L95" s="27" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="M95" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="N95" s="52"/>
+        <v>383</v>
+      </c>
+      <c r="N95" s="57"/>
       <c r="O95" s="50"/>
       <c r="P95" s="50" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q95" s="50"/>
+        <v>384</v>
+      </c>
+      <c r="Q95" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="96" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="52"/>
-      <c r="C96" s="52"/>
-      <c r="D96" s="52"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
       <c r="G96" s="31"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
+      <c r="J96" s="57"/>
+      <c r="K96" s="57"/>
       <c r="L96" s="27" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="M96" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="N96" s="52"/>
+        <v>386</v>
+      </c>
+      <c r="N96" s="57"/>
       <c r="O96" s="50"/>
       <c r="P96" s="50" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q96" s="50"/>
+        <v>387</v>
+      </c>
+      <c r="Q96" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="97" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B97" s="52"/>
-      <c r="C97" s="52"/>
-      <c r="D97" s="53"/>
-      <c r="E97" s="53"/>
-      <c r="F97" s="53"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54"/>
       <c r="G97" s="31"/>
-      <c r="H97" s="53"/>
-      <c r="I97" s="53"/>
-      <c r="J97" s="53"/>
-      <c r="K97" s="53"/>
+      <c r="H97" s="54"/>
+      <c r="I97" s="54"/>
+      <c r="J97" s="54"/>
+      <c r="K97" s="54"/>
       <c r="L97" s="27" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="M97" s="45" t="s">
-        <v>401</v>
-      </c>
-      <c r="N97" s="52"/>
+        <v>389</v>
+      </c>
+      <c r="N97" s="57"/>
       <c r="O97" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P97" s="50" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q97" s="50"/>
+        <v>390</v>
+      </c>
+      <c r="Q97" s="50" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="98" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
-      <c r="D98" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="E98" s="59" t="s">
-        <v>404</v>
-      </c>
-      <c r="F98" s="57" t="s">
-        <v>405</v>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="63" t="s">
+        <v>391</v>
+      </c>
+      <c r="E98" s="56" t="s">
+        <v>392</v>
+      </c>
+      <c r="F98" s="63" t="s">
+        <v>393</v>
       </c>
       <c r="G98" s="30"/>
-      <c r="H98" s="59" t="s">
+      <c r="H98" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I98" s="51" t="s">
-        <v>406</v>
-      </c>
-      <c r="J98" s="51" t="s">
-        <v>407</v>
-      </c>
-      <c r="K98" s="51" t="s">
+      <c r="I98" s="55" t="s">
+        <v>394</v>
+      </c>
+      <c r="J98" s="55" t="s">
+        <v>395</v>
+      </c>
+      <c r="K98" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L98" s="27" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="M98" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="N98" s="52"/>
+        <v>397</v>
+      </c>
+      <c r="N98" s="57"/>
       <c r="O98" s="50"/>
       <c r="P98" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q98" s="50"/>
+        <v>398</v>
+      </c>
+      <c r="Q98" s="50" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="99" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B99" s="52"/>
-      <c r="C99" s="52"/>
-      <c r="D99" s="52"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
       <c r="G99" s="31"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="52"/>
-      <c r="K99" s="52"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
+      <c r="J99" s="57"/>
+      <c r="K99" s="57"/>
       <c r="L99" s="27" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="M99" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="N99" s="52"/>
+        <v>400</v>
+      </c>
+      <c r="N99" s="57"/>
       <c r="O99" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P99" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q99" s="50"/>
+        <v>401</v>
+      </c>
+      <c r="Q99" s="50" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="100" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="52"/>
-      <c r="C100" s="52"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
       <c r="G100" s="31"/>
-      <c r="H100" s="52"/>
-      <c r="I100" s="52"/>
-      <c r="J100" s="52"/>
-      <c r="K100" s="52"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
       <c r="L100" s="27" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="M100" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="N100" s="52"/>
+        <v>403</v>
+      </c>
+      <c r="N100" s="57"/>
       <c r="O100" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P100" s="50" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="Q100" s="50" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
     </row>
     <row r="101" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B101" s="52"/>
-      <c r="C101" s="52"/>
-      <c r="D101" s="52"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="52"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
       <c r="G101" s="31"/>
-      <c r="H101" s="52"/>
-      <c r="I101" s="52"/>
-      <c r="J101" s="52"/>
-      <c r="K101" s="52"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
       <c r="L101" s="27" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>418</v>
-      </c>
-      <c r="N101" s="52"/>
+        <v>406</v>
+      </c>
+      <c r="N101" s="57"/>
       <c r="O101" s="50"/>
       <c r="P101" s="50" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="Q101" s="50" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="102" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B102" s="52"/>
-      <c r="C102" s="52"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="53"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="57"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="54"/>
       <c r="G102" s="31"/>
-      <c r="H102" s="53"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
+      <c r="H102" s="54"/>
+      <c r="I102" s="54"/>
+      <c r="J102" s="54"/>
+      <c r="K102" s="54"/>
       <c r="L102" s="27" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="M102" s="26" t="s">
-        <v>421</v>
-      </c>
-      <c r="N102" s="52"/>
+        <v>409</v>
+      </c>
+      <c r="N102" s="57"/>
       <c r="O102" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P102" s="50" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="Q102" s="50" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
     </row>
     <row r="103" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B103" s="52"/>
-      <c r="C103" s="52"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="57" t="s">
-        <v>423</v>
-      </c>
-      <c r="G103" s="55" t="s">
+      <c r="B103" s="57"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="57"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="63" t="s">
+        <v>411</v>
+      </c>
+      <c r="G103" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H103" s="55" t="s">
+      <c r="H103" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I103" s="51" t="s">
-        <v>424</v>
-      </c>
-      <c r="J103" s="51" t="s">
-        <v>425</v>
-      </c>
-      <c r="K103" s="51" t="s">
+      <c r="I103" s="55" t="s">
+        <v>412</v>
+      </c>
+      <c r="J103" s="55" t="s">
+        <v>413</v>
+      </c>
+      <c r="K103" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L103" s="27" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M103" s="26" t="s">
-        <v>427</v>
-      </c>
-      <c r="N103" s="52"/>
+        <v>415</v>
+      </c>
+      <c r="N103" s="57"/>
       <c r="O103" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P103" s="50" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="Q103" s="50" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
     </row>
     <row r="104" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
-      <c r="H104" s="52"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
+      <c r="B104" s="57"/>
+      <c r="C104" s="57"/>
+      <c r="D104" s="57"/>
+      <c r="E104" s="57"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="57"/>
+      <c r="H104" s="57"/>
+      <c r="I104" s="57"/>
+      <c r="J104" s="57"/>
+      <c r="K104" s="57"/>
       <c r="L104" s="27" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="M104" s="26" t="s">
-        <v>430</v>
-      </c>
-      <c r="N104" s="52"/>
+        <v>418</v>
+      </c>
+      <c r="N104" s="57"/>
       <c r="O104" s="50"/>
       <c r="P104" s="50" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="Q104" s="50" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="105" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B105" s="52"/>
-      <c r="C105" s="52"/>
-      <c r="D105" s="53"/>
-      <c r="E105" s="53"/>
-      <c r="F105" s="53"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="53"/>
-      <c r="I105" s="53"/>
-      <c r="J105" s="53"/>
-      <c r="K105" s="53"/>
+      <c r="B105" s="57"/>
+      <c r="C105" s="57"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="54"/>
+      <c r="G105" s="54"/>
+      <c r="H105" s="54"/>
+      <c r="I105" s="54"/>
+      <c r="J105" s="54"/>
+      <c r="K105" s="54"/>
       <c r="L105" s="27" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="M105" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="N105" s="52"/>
+        <v>421</v>
+      </c>
+      <c r="N105" s="57"/>
       <c r="O105" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P105" s="50" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="Q105" s="50" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
     </row>
     <row r="106" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B106" s="52"/>
-      <c r="C106" s="52"/>
-      <c r="D106" s="57" t="s">
-        <v>435</v>
-      </c>
-      <c r="E106" s="59" t="s">
-        <v>436</v>
-      </c>
-      <c r="F106" s="57" t="s">
-        <v>437</v>
+      <c r="B106" s="57"/>
+      <c r="C106" s="57"/>
+      <c r="D106" s="63" t="s">
+        <v>423</v>
+      </c>
+      <c r="E106" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="F106" s="63" t="s">
+        <v>425</v>
       </c>
       <c r="G106" s="12"/>
-      <c r="H106" s="59" t="s">
+      <c r="H106" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I106" s="51" t="s">
-        <v>438</v>
-      </c>
-      <c r="J106" s="51" t="s">
-        <v>439</v>
-      </c>
-      <c r="K106" s="51" t="s">
+      <c r="I106" s="55" t="s">
+        <v>426</v>
+      </c>
+      <c r="J106" s="55" t="s">
+        <v>427</v>
+      </c>
+      <c r="K106" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L106" s="22" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="M106" s="22" t="s">
-        <v>441</v>
-      </c>
-      <c r="N106" s="52"/>
+        <v>429</v>
+      </c>
+      <c r="N106" s="57"/>
       <c r="O106" s="50"/>
       <c r="P106" s="50" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="Q106" s="50" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="107" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="53"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="57"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="54"/>
       <c r="G107" s="13"/>
-      <c r="H107" s="53"/>
-      <c r="I107" s="53"/>
-      <c r="J107" s="53"/>
-      <c r="K107" s="53"/>
+      <c r="H107" s="54"/>
+      <c r="I107" s="54"/>
+      <c r="J107" s="54"/>
+      <c r="K107" s="54"/>
       <c r="L107" s="22" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="M107" s="26" t="s">
-        <v>444</v>
-      </c>
-      <c r="N107" s="52"/>
+        <v>432</v>
+      </c>
+      <c r="N107" s="57"/>
       <c r="O107" s="50"/>
       <c r="P107" s="50" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="Q107" s="50" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="108" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B108" s="52"/>
-      <c r="C108" s="52"/>
-      <c r="D108" s="52"/>
-      <c r="E108" s="52"/>
+      <c r="B108" s="57"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
       <c r="F108" s="20" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="G108" s="14"/>
       <c r="H108" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I108" s="22" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="J108" s="22" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="K108" s="22" t="s">
         <v>6</v>
       </c>
       <c r="L108" s="22" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="M108" s="26" t="s">
-        <v>450</v>
-      </c>
-      <c r="N108" s="52"/>
+        <v>438</v>
+      </c>
+      <c r="N108" s="57"/>
       <c r="O108" s="50"/>
       <c r="P108" s="50" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="Q108" s="50" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
     </row>
     <row r="109" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B109" s="52"/>
-      <c r="C109" s="52"/>
-      <c r="D109" s="52"/>
-      <c r="E109" s="52"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="57"/>
+      <c r="E109" s="57"/>
       <c r="F109" s="47" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="G109" s="11"/>
       <c r="H109" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="21" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="J109" s="21" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="K109" s="21" t="s">
         <v>6</v>
       </c>
       <c r="L109" s="22" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="M109" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="N109" s="52"/>
+        <v>444</v>
+      </c>
+      <c r="N109" s="57"/>
       <c r="O109" s="50"/>
       <c r="P109" s="50" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="Q109" s="50" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
     </row>
     <row r="110" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B110" s="52"/>
-      <c r="C110" s="52"/>
-      <c r="D110" s="52"/>
-      <c r="E110" s="52"/>
-      <c r="F110" s="57" t="s">
-        <v>458</v>
-      </c>
-      <c r="G110" s="55" t="s">
+      <c r="B110" s="57"/>
+      <c r="C110" s="57"/>
+      <c r="D110" s="57"/>
+      <c r="E110" s="57"/>
+      <c r="F110" s="63" t="s">
+        <v>446</v>
+      </c>
+      <c r="G110" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H110" s="55" t="s">
+      <c r="H110" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I110" s="51" t="s">
-        <v>459</v>
-      </c>
-      <c r="J110" s="51" t="s">
-        <v>460</v>
-      </c>
-      <c r="K110" s="51" t="s">
+      <c r="I110" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="J110" s="55" t="s">
+        <v>448</v>
+      </c>
+      <c r="K110" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L110" s="22" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="M110" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="N110" s="52"/>
+        <v>450</v>
+      </c>
+      <c r="N110" s="57"/>
       <c r="O110" s="50"/>
       <c r="P110" s="50" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Q110" s="50" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
     </row>
     <row r="111" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B111" s="52"/>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="52"/>
-      <c r="H111" s="52"/>
-      <c r="I111" s="52"/>
-      <c r="J111" s="52"/>
-      <c r="K111" s="52"/>
+      <c r="B111" s="57"/>
+      <c r="C111" s="57"/>
+      <c r="D111" s="57"/>
+      <c r="E111" s="57"/>
+      <c r="F111" s="57"/>
+      <c r="G111" s="57"/>
+      <c r="H111" s="57"/>
+      <c r="I111" s="57"/>
+      <c r="J111" s="57"/>
+      <c r="K111" s="57"/>
       <c r="L111" s="22" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="M111" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="N111" s="52"/>
+        <v>453</v>
+      </c>
+      <c r="N111" s="57"/>
       <c r="O111" s="50"/>
       <c r="P111" s="50" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="Q111" s="50" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
     </row>
     <row r="112" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B112" s="52"/>
-      <c r="C112" s="52"/>
-      <c r="D112" s="53"/>
-      <c r="E112" s="53"/>
-      <c r="F112" s="53"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="53"/>
-      <c r="I112" s="53"/>
-      <c r="J112" s="53"/>
-      <c r="K112" s="53"/>
+      <c r="B112" s="57"/>
+      <c r="C112" s="57"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="54"/>
+      <c r="J112" s="54"/>
+      <c r="K112" s="54"/>
       <c r="L112" s="22" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="N112" s="52"/>
+        <v>456</v>
+      </c>
+      <c r="N112" s="57"/>
       <c r="O112" s="50"/>
       <c r="P112" s="50" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q112" s="50"/>
+        <v>457</v>
+      </c>
+      <c r="Q112" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="113" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B113" s="52"/>
-      <c r="C113" s="52"/>
-      <c r="D113" s="57" t="s">
-        <v>470</v>
-      </c>
-      <c r="E113" s="59" t="s">
-        <v>471</v>
-      </c>
-      <c r="F113" s="57" t="s">
-        <v>472</v>
-      </c>
-      <c r="G113" s="55" t="s">
+      <c r="B113" s="57"/>
+      <c r="C113" s="57"/>
+      <c r="D113" s="63" t="s">
+        <v>458</v>
+      </c>
+      <c r="E113" s="56" t="s">
+        <v>459</v>
+      </c>
+      <c r="F113" s="63" t="s">
+        <v>460</v>
+      </c>
+      <c r="G113" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H113" s="59" t="s">
+      <c r="H113" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I113" s="51" t="s">
-        <v>473</v>
-      </c>
-      <c r="J113" s="51" t="s">
-        <v>474</v>
-      </c>
-      <c r="K113" s="51" t="s">
+      <c r="I113" s="55" t="s">
+        <v>461</v>
+      </c>
+      <c r="J113" s="55" t="s">
+        <v>462</v>
+      </c>
+      <c r="K113" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L113" s="22" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="M113" s="26" t="s">
-        <v>476</v>
-      </c>
-      <c r="N113" s="52"/>
+        <v>464</v>
+      </c>
+      <c r="N113" s="57"/>
       <c r="O113" s="50"/>
       <c r="P113" s="50" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q113" s="50"/>
+        <v>465</v>
+      </c>
+      <c r="Q113" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="114" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B114" s="52"/>
-      <c r="C114" s="52"/>
-      <c r="D114" s="52"/>
-      <c r="E114" s="52"/>
-      <c r="F114" s="52"/>
-      <c r="G114" s="52"/>
-      <c r="H114" s="52"/>
-      <c r="I114" s="52"/>
-      <c r="J114" s="52"/>
-      <c r="K114" s="52"/>
+      <c r="B114" s="57"/>
+      <c r="C114" s="57"/>
+      <c r="D114" s="57"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="57"/>
+      <c r="J114" s="57"/>
+      <c r="K114" s="57"/>
       <c r="L114" s="22" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="M114" s="26" t="s">
-        <v>479</v>
-      </c>
-      <c r="N114" s="52"/>
+        <v>467</v>
+      </c>
+      <c r="N114" s="57"/>
       <c r="O114" s="50"/>
       <c r="P114" s="50" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q114" s="50"/>
+        <v>468</v>
+      </c>
+      <c r="Q114" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="115" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B115" s="52"/>
-      <c r="C115" s="52"/>
-      <c r="D115" s="52"/>
-      <c r="E115" s="52"/>
-      <c r="F115" s="52"/>
-      <c r="G115" s="53"/>
-      <c r="H115" s="52"/>
-      <c r="I115" s="52"/>
-      <c r="J115" s="52"/>
-      <c r="K115" s="53"/>
+      <c r="B115" s="57"/>
+      <c r="C115" s="57"/>
+      <c r="D115" s="57"/>
+      <c r="E115" s="57"/>
+      <c r="F115" s="57"/>
+      <c r="G115" s="54"/>
+      <c r="H115" s="57"/>
+      <c r="I115" s="57"/>
+      <c r="J115" s="57"/>
+      <c r="K115" s="54"/>
       <c r="L115" s="22" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="N115" s="52"/>
+        <v>470</v>
+      </c>
+      <c r="N115" s="57"/>
       <c r="O115" s="50"/>
       <c r="P115" s="50" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q115" s="50"/>
+        <v>471</v>
+      </c>
+      <c r="Q115" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="116" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B116" s="52"/>
-      <c r="C116" s="52"/>
-      <c r="D116" s="52"/>
-      <c r="E116" s="52"/>
-      <c r="F116" s="52"/>
+      <c r="B116" s="57"/>
+      <c r="C116" s="57"/>
+      <c r="D116" s="57"/>
+      <c r="E116" s="57"/>
+      <c r="F116" s="57"/>
       <c r="G116" s="11"/>
-      <c r="H116" s="52"/>
-      <c r="I116" s="52"/>
-      <c r="J116" s="52"/>
-      <c r="K116" s="51" t="s">
+      <c r="H116" s="57"/>
+      <c r="I116" s="57"/>
+      <c r="J116" s="57"/>
+      <c r="K116" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L116" s="22" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="M116" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="N116" s="52"/>
+        <v>473</v>
+      </c>
+      <c r="N116" s="57"/>
       <c r="O116" s="50"/>
       <c r="P116" s="50" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q116" s="50"/>
+        <v>474</v>
+      </c>
+      <c r="Q116" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="117" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B117" s="52"/>
-      <c r="C117" s="52"/>
-      <c r="D117" s="52"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="52"/>
+      <c r="B117" s="57"/>
+      <c r="C117" s="57"/>
+      <c r="D117" s="57"/>
+      <c r="E117" s="57"/>
+      <c r="F117" s="57"/>
       <c r="G117" s="12"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="52"/>
-      <c r="J117" s="52"/>
-      <c r="K117" s="52"/>
+      <c r="H117" s="57"/>
+      <c r="I117" s="57"/>
+      <c r="J117" s="57"/>
+      <c r="K117" s="57"/>
       <c r="L117" s="22" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="M117" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="N117" s="52"/>
+        <v>476</v>
+      </c>
+      <c r="N117" s="57"/>
       <c r="O117" s="50"/>
       <c r="P117" s="50" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q117" s="50"/>
+        <v>477</v>
+      </c>
+      <c r="Q117" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="118" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B118" s="52"/>
-      <c r="C118" s="52"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="53"/>
+      <c r="B118" s="57"/>
+      <c r="C118" s="57"/>
+      <c r="D118" s="57"/>
+      <c r="E118" s="57"/>
+      <c r="F118" s="54"/>
       <c r="G118" s="13"/>
-      <c r="H118" s="53"/>
-      <c r="I118" s="53"/>
-      <c r="J118" s="53"/>
-      <c r="K118" s="53"/>
+      <c r="H118" s="54"/>
+      <c r="I118" s="54"/>
+      <c r="J118" s="54"/>
+      <c r="K118" s="54"/>
       <c r="L118" s="22" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="M118" s="26" t="s">
-        <v>491</v>
-      </c>
-      <c r="N118" s="52"/>
+        <v>479</v>
+      </c>
+      <c r="N118" s="57"/>
       <c r="O118" s="50"/>
       <c r="P118" s="50" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="Q118" s="50" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
     </row>
     <row r="119" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B119" s="52"/>
-      <c r="C119" s="52"/>
-      <c r="D119" s="52"/>
-      <c r="E119" s="52"/>
+      <c r="B119" s="57"/>
+      <c r="C119" s="57"/>
+      <c r="D119" s="57"/>
+      <c r="E119" s="57"/>
       <c r="F119" s="19" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G119" s="11"/>
       <c r="H119" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I119" s="23" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="J119" s="23" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="K119" s="23" t="s">
         <v>6</v>
       </c>
       <c r="L119" s="22" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M119" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="N119" s="52"/>
+        <v>646</v>
+      </c>
+      <c r="N119" s="57"/>
       <c r="O119" s="50"/>
       <c r="P119" s="50" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q119" s="50"/>
+        <v>485</v>
+      </c>
+      <c r="Q119" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="120" spans="2:17" ht="234" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B120" s="52"/>
-      <c r="C120" s="52"/>
-      <c r="D120" s="52"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="57" t="s">
-        <v>498</v>
+      <c r="B120" s="57"/>
+      <c r="C120" s="57"/>
+      <c r="D120" s="57"/>
+      <c r="E120" s="57"/>
+      <c r="F120" s="63" t="s">
+        <v>486</v>
       </c>
       <c r="G120" s="11"/>
-      <c r="H120" s="59" t="s">
+      <c r="H120" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I120" s="51" t="s">
-        <v>499</v>
-      </c>
-      <c r="J120" s="51" t="s">
-        <v>500</v>
-      </c>
-      <c r="K120" s="51" t="s">
+      <c r="I120" s="55" t="s">
+        <v>487</v>
+      </c>
+      <c r="J120" s="55" t="s">
+        <v>488</v>
+      </c>
+      <c r="K120" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L120" s="22" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="M120" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="N120" s="52"/>
+        <v>490</v>
+      </c>
+      <c r="N120" s="57"/>
       <c r="O120" s="50" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="P120" s="50" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q120" s="50"/>
+        <v>492</v>
+      </c>
+      <c r="Q120" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="121" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B121" s="52"/>
-      <c r="C121" s="52"/>
-      <c r="D121" s="52"/>
-      <c r="E121" s="52"/>
-      <c r="F121" s="52"/>
+      <c r="B121" s="57"/>
+      <c r="C121" s="57"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="57"/>
+      <c r="F121" s="57"/>
       <c r="G121" s="12"/>
-      <c r="H121" s="52"/>
-      <c r="I121" s="52"/>
-      <c r="J121" s="52"/>
-      <c r="K121" s="52"/>
+      <c r="H121" s="57"/>
+      <c r="I121" s="57"/>
+      <c r="J121" s="57"/>
+      <c r="K121" s="57"/>
       <c r="L121" s="22" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M121" s="26" t="s">
-        <v>506</v>
-      </c>
-      <c r="N121" s="52"/>
+        <v>494</v>
+      </c>
+      <c r="N121" s="57"/>
       <c r="O121" s="50"/>
       <c r="P121" s="50" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q121" s="50"/>
+        <v>495</v>
+      </c>
+      <c r="Q121" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="122" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B122" s="52"/>
-      <c r="C122" s="52"/>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="53"/>
+      <c r="B122" s="57"/>
+      <c r="C122" s="57"/>
+      <c r="D122" s="57"/>
+      <c r="E122" s="57"/>
+      <c r="F122" s="54"/>
       <c r="G122" s="12"/>
-      <c r="H122" s="53"/>
-      <c r="I122" s="53"/>
-      <c r="J122" s="53"/>
-      <c r="K122" s="53"/>
+      <c r="H122" s="54"/>
+      <c r="I122" s="54"/>
+      <c r="J122" s="54"/>
+      <c r="K122" s="54"/>
       <c r="L122" s="22" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="M122" s="26" t="s">
-        <v>509</v>
-      </c>
-      <c r="N122" s="52"/>
+        <v>497</v>
+      </c>
+      <c r="N122" s="57"/>
       <c r="O122" s="50" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="P122" s="50" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q122" s="50"/>
+        <v>499</v>
+      </c>
+      <c r="Q122" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="123" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B123" s="52"/>
-      <c r="C123" s="52"/>
-      <c r="D123" s="52"/>
-      <c r="E123" s="52"/>
-      <c r="F123" s="57" t="s">
-        <v>512</v>
-      </c>
-      <c r="G123" s="55" t="s">
+      <c r="B123" s="57"/>
+      <c r="C123" s="57"/>
+      <c r="D123" s="57"/>
+      <c r="E123" s="57"/>
+      <c r="F123" s="63" t="s">
+        <v>500</v>
+      </c>
+      <c r="G123" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H123" s="55" t="s">
+      <c r="H123" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="I123" s="51" t="s">
-        <v>513</v>
-      </c>
-      <c r="J123" s="51" t="s">
-        <v>514</v>
-      </c>
-      <c r="K123" s="51" t="s">
+      <c r="I123" s="55" t="s">
+        <v>501</v>
+      </c>
+      <c r="J123" s="55" t="s">
+        <v>502</v>
+      </c>
+      <c r="K123" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L123" s="27" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="M123" s="26" t="s">
-        <v>516</v>
-      </c>
-      <c r="N123" s="52"/>
+        <v>504</v>
+      </c>
+      <c r="N123" s="57"/>
       <c r="O123" s="50"/>
       <c r="P123" s="50" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q123" s="50"/>
+        <v>505</v>
+      </c>
+      <c r="Q123" s="50" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="124" spans="2:17" ht="390" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B124" s="52"/>
-      <c r="C124" s="52"/>
-      <c r="D124" s="52"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="53"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="53"/>
+      <c r="B124" s="57"/>
+      <c r="C124" s="57"/>
+      <c r="D124" s="57"/>
+      <c r="E124" s="57"/>
+      <c r="F124" s="57"/>
+      <c r="G124" s="54"/>
+      <c r="H124" s="57"/>
+      <c r="I124" s="57"/>
+      <c r="J124" s="57"/>
+      <c r="K124" s="54"/>
       <c r="L124" s="27" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="M124" s="26" t="s">
-        <v>519</v>
-      </c>
-      <c r="N124" s="52"/>
+        <v>507</v>
+      </c>
+      <c r="N124" s="57"/>
       <c r="O124" s="50" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="P124" s="50" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="Q124" s="50" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
     </row>
     <row r="125" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B125" s="52"/>
-      <c r="C125" s="52"/>
-      <c r="D125" s="52"/>
-      <c r="E125" s="52"/>
-      <c r="F125" s="53"/>
+      <c r="B125" s="57"/>
+      <c r="C125" s="57"/>
+      <c r="D125" s="57"/>
+      <c r="E125" s="57"/>
+      <c r="F125" s="54"/>
       <c r="G125" s="49"/>
-      <c r="H125" s="53"/>
-      <c r="I125" s="53"/>
-      <c r="J125" s="53"/>
+      <c r="H125" s="54"/>
+      <c r="I125" s="54"/>
+      <c r="J125" s="54"/>
       <c r="K125" s="48" t="s">
         <v>6</v>
       </c>
       <c r="L125" s="27" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M125" s="26" t="s">
-        <v>662</v>
-      </c>
-      <c r="N125" s="52"/>
+        <v>649</v>
+      </c>
+      <c r="N125" s="57"/>
       <c r="O125" s="50"/>
       <c r="P125" s="50" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="Q125" s="50" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
     </row>
     <row r="126" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B126" s="52"/>
-      <c r="C126" s="52"/>
-      <c r="D126" s="52"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="74" t="s">
-        <v>523</v>
-      </c>
-      <c r="G126" s="55" t="s">
+      <c r="B126" s="57"/>
+      <c r="C126" s="57"/>
+      <c r="D126" s="57"/>
+      <c r="E126" s="57"/>
+      <c r="F126" s="67" t="s">
+        <v>511</v>
+      </c>
+      <c r="G126" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H126" s="59" t="s">
+      <c r="H126" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I126" s="51" t="s">
-        <v>524</v>
-      </c>
-      <c r="J126" s="51" t="s">
-        <v>525</v>
-      </c>
-      <c r="K126" s="51" t="s">
+      <c r="I126" s="55" t="s">
+        <v>512</v>
+      </c>
+      <c r="J126" s="55" t="s">
+        <v>513</v>
+      </c>
+      <c r="K126" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="M126" s="26" t="s">
-        <v>527</v>
-      </c>
-      <c r="N126" s="52"/>
+        <v>515</v>
+      </c>
+      <c r="N126" s="57"/>
       <c r="O126" s="50"/>
       <c r="P126" s="50" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="Q126" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="127" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B127" s="52"/>
-      <c r="C127" s="52"/>
-      <c r="D127" s="52"/>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
+      <c r="B127" s="57"/>
+      <c r="C127" s="57"/>
+      <c r="D127" s="57"/>
+      <c r="E127" s="57"/>
+      <c r="F127" s="57"/>
+      <c r="G127" s="57"/>
+      <c r="H127" s="57"/>
+      <c r="I127" s="57"/>
+      <c r="J127" s="57"/>
+      <c r="K127" s="57"/>
       <c r="L127" s="22" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="M127" s="26" t="s">
-        <v>529</v>
-      </c>
-      <c r="N127" s="52"/>
+        <v>517</v>
+      </c>
+      <c r="N127" s="57"/>
       <c r="O127" s="50"/>
       <c r="P127" s="50" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="Q127" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="128" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B128" s="52"/>
-      <c r="C128" s="52"/>
-      <c r="D128" s="52"/>
-      <c r="E128" s="52"/>
-      <c r="F128" s="52"/>
-      <c r="G128" s="53"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="52"/>
-      <c r="J128" s="52"/>
-      <c r="K128" s="53"/>
+      <c r="B128" s="57"/>
+      <c r="C128" s="57"/>
+      <c r="D128" s="57"/>
+      <c r="E128" s="57"/>
+      <c r="F128" s="57"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="57"/>
+      <c r="I128" s="57"/>
+      <c r="J128" s="57"/>
+      <c r="K128" s="54"/>
       <c r="L128" s="22" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="M128" s="26" t="s">
-        <v>532</v>
-      </c>
-      <c r="N128" s="52"/>
+        <v>520</v>
+      </c>
+      <c r="N128" s="57"/>
       <c r="O128" s="50"/>
       <c r="P128" s="50" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="Q128" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="129" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B129" s="52"/>
-      <c r="C129" s="52"/>
-      <c r="D129" s="52"/>
-      <c r="E129" s="52"/>
-      <c r="F129" s="52"/>
+      <c r="B129" s="57"/>
+      <c r="C129" s="57"/>
+      <c r="D129" s="57"/>
+      <c r="E129" s="57"/>
+      <c r="F129" s="57"/>
       <c r="G129" s="11"/>
-      <c r="H129" s="52"/>
-      <c r="I129" s="52"/>
-      <c r="J129" s="52"/>
-      <c r="K129" s="51" t="s">
+      <c r="H129" s="57"/>
+      <c r="I129" s="57"/>
+      <c r="J129" s="57"/>
+      <c r="K129" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L129" s="27" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="M129" s="26" t="s">
-        <v>535</v>
-      </c>
-      <c r="N129" s="52"/>
+        <v>523</v>
+      </c>
+      <c r="N129" s="57"/>
       <c r="O129" s="50"/>
       <c r="P129" s="50" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="Q129" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="130" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B130" s="52"/>
-      <c r="C130" s="52"/>
-      <c r="D130" s="53"/>
-      <c r="E130" s="53"/>
-      <c r="F130" s="53"/>
+      <c r="B130" s="57"/>
+      <c r="C130" s="57"/>
+      <c r="D130" s="54"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
       <c r="G130" s="13"/>
-      <c r="H130" s="53"/>
-      <c r="I130" s="53"/>
-      <c r="J130" s="53"/>
-      <c r="K130" s="53"/>
+      <c r="H130" s="54"/>
+      <c r="I130" s="54"/>
+      <c r="J130" s="54"/>
+      <c r="K130" s="54"/>
       <c r="L130" s="27" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="M130" s="26" t="s">
-        <v>538</v>
-      </c>
-      <c r="N130" s="52"/>
+        <v>526</v>
+      </c>
+      <c r="N130" s="57"/>
       <c r="O130" s="50"/>
       <c r="P130" s="50" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="Q130" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="131" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B131" s="52"/>
-      <c r="C131" s="52"/>
-      <c r="D131" s="57" t="s">
-        <v>540</v>
-      </c>
-      <c r="E131" s="59" t="s">
-        <v>541</v>
-      </c>
-      <c r="F131" s="57" t="s">
-        <v>542</v>
-      </c>
-      <c r="G131" s="55" t="s">
+      <c r="B131" s="57"/>
+      <c r="C131" s="57"/>
+      <c r="D131" s="63" t="s">
+        <v>528</v>
+      </c>
+      <c r="E131" s="56" t="s">
+        <v>529</v>
+      </c>
+      <c r="F131" s="63" t="s">
+        <v>530</v>
+      </c>
+      <c r="G131" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H131" s="59" t="s">
+      <c r="H131" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="I131" s="51" t="s">
-        <v>543</v>
-      </c>
-      <c r="J131" s="51" t="s">
-        <v>544</v>
-      </c>
-      <c r="K131" s="51" t="s">
+      <c r="I131" s="55" t="s">
+        <v>531</v>
+      </c>
+      <c r="J131" s="55" t="s">
+        <v>532</v>
+      </c>
+      <c r="K131" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L131" s="22" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="M131" s="26" t="s">
-        <v>546</v>
-      </c>
-      <c r="N131" s="52"/>
+        <v>534</v>
+      </c>
+      <c r="N131" s="57"/>
       <c r="O131" s="50"/>
       <c r="P131" s="50" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="Q131" s="50" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
     </row>
     <row r="132" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B132" s="52"/>
-      <c r="C132" s="52"/>
-      <c r="D132" s="52"/>
-      <c r="E132" s="52"/>
-      <c r="F132" s="52"/>
-      <c r="G132" s="52"/>
-      <c r="H132" s="52"/>
-      <c r="I132" s="52"/>
-      <c r="J132" s="52"/>
-      <c r="K132" s="52"/>
+      <c r="B132" s="57"/>
+      <c r="C132" s="57"/>
+      <c r="D132" s="57"/>
+      <c r="E132" s="57"/>
+      <c r="F132" s="57"/>
+      <c r="G132" s="57"/>
+      <c r="H132" s="57"/>
+      <c r="I132" s="57"/>
+      <c r="J132" s="57"/>
+      <c r="K132" s="57"/>
       <c r="L132" s="22" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="M132" s="26" t="s">
-        <v>549</v>
-      </c>
-      <c r="N132" s="52"/>
+        <v>537</v>
+      </c>
+      <c r="N132" s="57"/>
       <c r="O132" s="50"/>
       <c r="P132" s="50" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="Q132" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="133" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B133" s="52"/>
-      <c r="C133" s="52"/>
-      <c r="D133" s="52"/>
-      <c r="E133" s="52"/>
-      <c r="F133" s="52"/>
-      <c r="G133" s="52"/>
-      <c r="H133" s="52"/>
-      <c r="I133" s="52"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
+      <c r="B133" s="57"/>
+      <c r="C133" s="57"/>
+      <c r="D133" s="57"/>
+      <c r="E133" s="57"/>
+      <c r="F133" s="57"/>
+      <c r="G133" s="57"/>
+      <c r="H133" s="57"/>
+      <c r="I133" s="57"/>
+      <c r="J133" s="57"/>
+      <c r="K133" s="57"/>
       <c r="L133" s="22" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="M133" s="26" t="s">
-        <v>552</v>
-      </c>
-      <c r="N133" s="52"/>
+        <v>540</v>
+      </c>
+      <c r="N133" s="57"/>
       <c r="O133" s="50"/>
       <c r="P133" s="50" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="Q133" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="134" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B134" s="52"/>
-      <c r="C134" s="52"/>
-      <c r="D134" s="52"/>
-      <c r="E134" s="52"/>
-      <c r="F134" s="52"/>
-      <c r="G134" s="52"/>
-      <c r="H134" s="52"/>
-      <c r="I134" s="52"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
+      <c r="B134" s="57"/>
+      <c r="C134" s="57"/>
+      <c r="D134" s="57"/>
+      <c r="E134" s="57"/>
+      <c r="F134" s="57"/>
+      <c r="G134" s="57"/>
+      <c r="H134" s="57"/>
+      <c r="I134" s="57"/>
+      <c r="J134" s="57"/>
+      <c r="K134" s="57"/>
       <c r="L134" s="22" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="M134" s="26" t="s">
-        <v>555</v>
-      </c>
-      <c r="N134" s="52"/>
+        <v>543</v>
+      </c>
+      <c r="N134" s="57"/>
       <c r="O134" s="50"/>
       <c r="P134" s="50" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="Q134" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="135" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B135" s="52"/>
-      <c r="C135" s="52"/>
-      <c r="D135" s="52"/>
-      <c r="E135" s="52"/>
-      <c r="F135" s="52"/>
-      <c r="G135" s="52"/>
-      <c r="H135" s="52"/>
-      <c r="I135" s="52"/>
-      <c r="J135" s="52"/>
-      <c r="K135" s="52"/>
+      <c r="B135" s="57"/>
+      <c r="C135" s="57"/>
+      <c r="D135" s="57"/>
+      <c r="E135" s="57"/>
+      <c r="F135" s="57"/>
+      <c r="G135" s="57"/>
+      <c r="H135" s="57"/>
+      <c r="I135" s="57"/>
+      <c r="J135" s="57"/>
+      <c r="K135" s="57"/>
       <c r="L135" s="22" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="M135" s="26" t="s">
-        <v>558</v>
-      </c>
-      <c r="N135" s="52"/>
+        <v>546</v>
+      </c>
+      <c r="N135" s="57"/>
       <c r="O135" s="50"/>
       <c r="P135" s="50" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="Q135" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="136" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="52"/>
-      <c r="C136" s="52"/>
-      <c r="D136" s="52"/>
-      <c r="E136" s="52"/>
-      <c r="F136" s="52"/>
-      <c r="G136" s="52"/>
-      <c r="H136" s="52"/>
-      <c r="I136" s="52"/>
-      <c r="J136" s="52"/>
-      <c r="K136" s="52"/>
+      <c r="B136" s="57"/>
+      <c r="C136" s="57"/>
+      <c r="D136" s="57"/>
+      <c r="E136" s="57"/>
+      <c r="F136" s="57"/>
+      <c r="G136" s="57"/>
+      <c r="H136" s="57"/>
+      <c r="I136" s="57"/>
+      <c r="J136" s="57"/>
+      <c r="K136" s="57"/>
       <c r="L136" s="22" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="M136" s="26" t="s">
-        <v>561</v>
-      </c>
-      <c r="N136" s="52"/>
+        <v>549</v>
+      </c>
+      <c r="N136" s="57"/>
       <c r="O136" s="50"/>
       <c r="P136" s="50" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="Q136" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="137" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="52"/>
-      <c r="C137" s="52"/>
-      <c r="D137" s="52"/>
-      <c r="E137" s="52"/>
-      <c r="F137" s="52"/>
-      <c r="G137" s="53"/>
-      <c r="H137" s="52"/>
-      <c r="I137" s="52"/>
-      <c r="J137" s="52"/>
-      <c r="K137" s="53"/>
+      <c r="B137" s="57"/>
+      <c r="C137" s="57"/>
+      <c r="D137" s="57"/>
+      <c r="E137" s="57"/>
+      <c r="F137" s="57"/>
+      <c r="G137" s="54"/>
+      <c r="H137" s="57"/>
+      <c r="I137" s="57"/>
+      <c r="J137" s="57"/>
+      <c r="K137" s="54"/>
       <c r="L137" s="22" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="M137" s="26" t="s">
-        <v>564</v>
-      </c>
-      <c r="N137" s="52"/>
+        <v>552</v>
+      </c>
+      <c r="N137" s="57"/>
       <c r="O137" s="50"/>
       <c r="P137" s="50" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="Q137" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="138" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="52"/>
-      <c r="C138" s="52"/>
-      <c r="D138" s="52"/>
-      <c r="E138" s="52"/>
-      <c r="F138" s="52"/>
+      <c r="B138" s="57"/>
+      <c r="C138" s="57"/>
+      <c r="D138" s="57"/>
+      <c r="E138" s="57"/>
+      <c r="F138" s="57"/>
       <c r="G138" s="11"/>
-      <c r="H138" s="52"/>
-      <c r="I138" s="52"/>
-      <c r="J138" s="52"/>
-      <c r="K138" s="51" t="s">
+      <c r="H138" s="57"/>
+      <c r="I138" s="57"/>
+      <c r="J138" s="57"/>
+      <c r="K138" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L138" s="22" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="M138" s="26" t="s">
-        <v>567</v>
-      </c>
-      <c r="N138" s="52"/>
+        <v>555</v>
+      </c>
+      <c r="N138" s="57"/>
       <c r="O138" s="50"/>
       <c r="P138" s="50" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="Q138" s="50" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="139" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="53"/>
-      <c r="C139" s="53"/>
-      <c r="D139" s="53"/>
-      <c r="E139" s="53"/>
-      <c r="F139" s="53"/>
+      <c r="B139" s="54"/>
+      <c r="C139" s="54"/>
+      <c r="D139" s="54"/>
+      <c r="E139" s="54"/>
+      <c r="F139" s="54"/>
       <c r="G139" s="13"/>
-      <c r="H139" s="53"/>
-      <c r="I139" s="53"/>
-      <c r="J139" s="53"/>
-      <c r="K139" s="53"/>
+      <c r="H139" s="54"/>
+      <c r="I139" s="54"/>
+      <c r="J139" s="54"/>
+      <c r="K139" s="54"/>
       <c r="L139" s="22" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="M139" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="N139" s="53"/>
+        <v>558</v>
+      </c>
+      <c r="N139" s="54"/>
       <c r="O139" s="50"/>
       <c r="P139" s="50" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="Q139" s="50" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
     </row>
     <row r="140" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="56">
+      <c r="B140" s="65">
         <v>5</v>
       </c>
-      <c r="C140" s="56" t="s">
-        <v>572</v>
-      </c>
-      <c r="D140" s="54" t="s">
-        <v>573</v>
-      </c>
-      <c r="E140" s="56" t="s">
-        <v>574</v>
-      </c>
-      <c r="F140" s="54" t="s">
-        <v>575</v>
-      </c>
-      <c r="G140" s="56" t="s">
+      <c r="C140" s="65" t="s">
+        <v>560</v>
+      </c>
+      <c r="D140" s="69" t="s">
+        <v>561</v>
+      </c>
+      <c r="E140" s="65" t="s">
+        <v>562</v>
+      </c>
+      <c r="F140" s="69" t="s">
+        <v>563</v>
+      </c>
+      <c r="G140" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="H140" s="56" t="s">
+      <c r="H140" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I140" s="51" t="s">
-        <v>576</v>
-      </c>
-      <c r="J140" s="51" t="s">
-        <v>577</v>
-      </c>
-      <c r="K140" s="51" t="s">
+      <c r="I140" s="55" t="s">
+        <v>564</v>
+      </c>
+      <c r="J140" s="55" t="s">
+        <v>565</v>
+      </c>
+      <c r="K140" s="55" t="s">
         <v>5</v>
       </c>
       <c r="L140" s="27" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="M140" s="26" t="s">
-        <v>579</v>
-      </c>
-      <c r="N140" s="62" t="s">
-        <v>580</v>
+        <v>567</v>
+      </c>
+      <c r="N140" s="74" t="s">
+        <v>568</v>
       </c>
       <c r="O140" s="50"/>
       <c r="P140" s="50" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="Q140" s="50" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
     </row>
     <row r="141" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B141" s="52"/>
-      <c r="C141" s="52"/>
-      <c r="D141" s="52"/>
-      <c r="E141" s="52"/>
-      <c r="F141" s="52"/>
-      <c r="G141" s="52"/>
-      <c r="H141" s="52"/>
-      <c r="I141" s="52"/>
-      <c r="J141" s="52"/>
-      <c r="K141" s="52"/>
+      <c r="B141" s="57"/>
+      <c r="C141" s="57"/>
+      <c r="D141" s="57"/>
+      <c r="E141" s="57"/>
+      <c r="F141" s="57"/>
+      <c r="G141" s="57"/>
+      <c r="H141" s="57"/>
+      <c r="I141" s="57"/>
+      <c r="J141" s="57"/>
+      <c r="K141" s="57"/>
       <c r="L141" s="27" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="M141" s="26" t="s">
-        <v>583</v>
-      </c>
-      <c r="N141" s="52"/>
+        <v>571</v>
+      </c>
+      <c r="N141" s="57"/>
       <c r="O141" s="50"/>
       <c r="P141" s="50" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="Q141" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="142" spans="2:17" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B142" s="52"/>
-      <c r="C142" s="52"/>
-      <c r="D142" s="52"/>
-      <c r="E142" s="52"/>
-      <c r="F142" s="53"/>
-      <c r="G142" s="53"/>
-      <c r="H142" s="53"/>
-      <c r="I142" s="53"/>
-      <c r="J142" s="53"/>
-      <c r="K142" s="53"/>
+      <c r="B142" s="57"/>
+      <c r="C142" s="57"/>
+      <c r="D142" s="57"/>
+      <c r="E142" s="57"/>
+      <c r="F142" s="54"/>
+      <c r="G142" s="54"/>
+      <c r="H142" s="54"/>
+      <c r="I142" s="54"/>
+      <c r="J142" s="54"/>
+      <c r="K142" s="54"/>
       <c r="L142" s="27" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="M142" s="26" t="s">
-        <v>585</v>
-      </c>
-      <c r="N142" s="52"/>
+        <v>573</v>
+      </c>
+      <c r="N142" s="57"/>
       <c r="O142" s="50"/>
       <c r="P142" s="50" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="Q142" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="143" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B143" s="52"/>
-      <c r="C143" s="52"/>
-      <c r="D143" s="52"/>
-      <c r="E143" s="52"/>
-      <c r="F143" s="54" t="s">
-        <v>587</v>
+      <c r="B143" s="57"/>
+      <c r="C143" s="57"/>
+      <c r="D143" s="57"/>
+      <c r="E143" s="57"/>
+      <c r="F143" s="69" t="s">
+        <v>575</v>
       </c>
       <c r="G143" s="15"/>
-      <c r="H143" s="56" t="s">
+      <c r="H143" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I143" s="51" t="s">
-        <v>588</v>
-      </c>
-      <c r="J143" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="K143" s="51" t="s">
+      <c r="I143" s="55" t="s">
+        <v>576</v>
+      </c>
+      <c r="J143" s="55" t="s">
+        <v>577</v>
+      </c>
+      <c r="K143" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L143" s="22" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="M143" s="22" t="s">
-        <v>591</v>
-      </c>
-      <c r="N143" s="52"/>
+        <v>579</v>
+      </c>
+      <c r="N143" s="57"/>
       <c r="O143" s="50"/>
       <c r="P143" s="50" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="Q143" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="144" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B144" s="52"/>
-      <c r="C144" s="52"/>
-      <c r="D144" s="52"/>
-      <c r="E144" s="52"/>
-      <c r="F144" s="52"/>
+      <c r="B144" s="57"/>
+      <c r="C144" s="57"/>
+      <c r="D144" s="57"/>
+      <c r="E144" s="57"/>
+      <c r="F144" s="57"/>
       <c r="G144" s="16"/>
-      <c r="H144" s="52"/>
-      <c r="I144" s="52"/>
-      <c r="J144" s="52"/>
-      <c r="K144" s="52"/>
+      <c r="H144" s="57"/>
+      <c r="I144" s="57"/>
+      <c r="J144" s="57"/>
+      <c r="K144" s="57"/>
       <c r="L144" s="22" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="M144" s="26" t="s">
-        <v>594</v>
-      </c>
-      <c r="N144" s="52"/>
+        <v>582</v>
+      </c>
+      <c r="N144" s="57"/>
       <c r="O144" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P144" s="50" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q144" s="50"/>
+        <v>583</v>
+      </c>
+      <c r="Q144" s="50" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="145" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B145" s="52"/>
-      <c r="C145" s="52"/>
-      <c r="D145" s="53"/>
-      <c r="E145" s="53"/>
-      <c r="F145" s="53"/>
+      <c r="B145" s="57"/>
+      <c r="C145" s="57"/>
+      <c r="D145" s="54"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="54"/>
       <c r="G145" s="17"/>
-      <c r="H145" s="53"/>
-      <c r="I145" s="53"/>
-      <c r="J145" s="53"/>
-      <c r="K145" s="53"/>
+      <c r="H145" s="54"/>
+      <c r="I145" s="54"/>
+      <c r="J145" s="54"/>
+      <c r="K145" s="54"/>
       <c r="L145" s="22" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="M145" s="26" t="s">
-        <v>597</v>
-      </c>
-      <c r="N145" s="52"/>
+        <v>585</v>
+      </c>
+      <c r="N145" s="57"/>
       <c r="O145" s="50"/>
       <c r="P145" s="50" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="Q145" s="50" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="146" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B146" s="52"/>
-      <c r="C146" s="52"/>
-      <c r="D146" s="54" t="s">
-        <v>599</v>
-      </c>
-      <c r="E146" s="56" t="s">
-        <v>600</v>
-      </c>
-      <c r="F146" s="54" t="s">
-        <v>601</v>
+      <c r="B146" s="57"/>
+      <c r="C146" s="57"/>
+      <c r="D146" s="69" t="s">
+        <v>587</v>
+      </c>
+      <c r="E146" s="65" t="s">
+        <v>588</v>
+      </c>
+      <c r="F146" s="69" t="s">
+        <v>589</v>
       </c>
       <c r="G146" s="15"/>
-      <c r="H146" s="56" t="s">
+      <c r="H146" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I146" s="51" t="s">
-        <v>602</v>
-      </c>
-      <c r="J146" s="51" t="s">
-        <v>603</v>
-      </c>
-      <c r="K146" s="51" t="s">
+      <c r="I146" s="55" t="s">
+        <v>590</v>
+      </c>
+      <c r="J146" s="55" t="s">
+        <v>591</v>
+      </c>
+      <c r="K146" s="55" t="s">
         <v>6</v>
       </c>
       <c r="L146" s="22" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="M146" s="26" t="s">
-        <v>605</v>
-      </c>
-      <c r="N146" s="52"/>
+        <v>593</v>
+      </c>
+      <c r="N146" s="57"/>
       <c r="O146" s="50"/>
       <c r="P146" s="50" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="Q146" s="50" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
     </row>
     <row r="147" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B147" s="53"/>
-      <c r="C147" s="53"/>
-      <c r="D147" s="53"/>
-      <c r="E147" s="53"/>
-      <c r="F147" s="53"/>
+      <c r="B147" s="54"/>
+      <c r="C147" s="54"/>
+      <c r="D147" s="54"/>
+      <c r="E147" s="54"/>
+      <c r="F147" s="54"/>
       <c r="G147" s="17"/>
-      <c r="H147" s="53"/>
-      <c r="I147" s="53"/>
-      <c r="J147" s="53"/>
-      <c r="K147" s="53"/>
+      <c r="H147" s="54"/>
+      <c r="I147" s="54"/>
+      <c r="J147" s="54"/>
+      <c r="K147" s="54"/>
       <c r="L147" s="22" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="M147" s="26" t="s">
-        <v>608</v>
-      </c>
-      <c r="N147" s="53"/>
+        <v>596</v>
+      </c>
+      <c r="N147" s="54"/>
       <c r="O147" s="50"/>
       <c r="P147" s="50" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="Q147" s="50" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
     </row>
     <row r="148" spans="2:17" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B148" s="61">
+      <c r="B148" s="73">
         <v>6</v>
       </c>
-      <c r="C148" s="61" t="s">
-        <v>610</v>
-      </c>
-      <c r="D148" s="73" t="s">
-        <v>611</v>
-      </c>
-      <c r="E148" s="61" t="s">
-        <v>612</v>
-      </c>
-      <c r="F148" s="73" t="s">
-        <v>613</v>
-      </c>
-      <c r="G148" s="67" t="s">
+      <c r="C148" s="73" t="s">
+        <v>598</v>
+      </c>
+      <c r="D148" s="66" t="s">
+        <v>599</v>
+      </c>
+      <c r="E148" s="73" t="s">
+        <v>600</v>
+      </c>
+      <c r="F148" s="66" t="s">
+        <v>601</v>
+      </c>
+      <c r="G148" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="H148" s="67" t="s">
+      <c r="H148" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="I148" s="70" t="s">
-        <v>614</v>
-      </c>
-      <c r="J148" s="70" t="s">
-        <v>615</v>
-      </c>
-      <c r="K148" s="70" t="s">
+      <c r="I148" s="72" t="s">
+        <v>602</v>
+      </c>
+      <c r="J148" s="72" t="s">
+        <v>603</v>
+      </c>
+      <c r="K148" s="72" t="s">
         <v>5</v>
       </c>
       <c r="L148" s="22" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="M148" s="26" t="s">
-        <v>617</v>
-      </c>
-      <c r="N148" s="61" t="s">
-        <v>618</v>
+        <v>605</v>
+      </c>
+      <c r="N148" s="73" t="s">
+        <v>606</v>
       </c>
       <c r="O148" s="50"/>
       <c r="P148" s="50" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="Q148" s="50" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="149" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B149" s="52"/>
-      <c r="C149" s="52"/>
-      <c r="D149" s="52"/>
-      <c r="E149" s="52"/>
-      <c r="F149" s="52"/>
-      <c r="G149" s="52"/>
-      <c r="H149" s="52"/>
-      <c r="I149" s="52"/>
-      <c r="J149" s="52"/>
-      <c r="K149" s="52"/>
+      <c r="B149" s="57"/>
+      <c r="C149" s="57"/>
+      <c r="D149" s="57"/>
+      <c r="E149" s="57"/>
+      <c r="F149" s="57"/>
+      <c r="G149" s="57"/>
+      <c r="H149" s="57"/>
+      <c r="I149" s="57"/>
+      <c r="J149" s="57"/>
+      <c r="K149" s="57"/>
       <c r="L149" s="22" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="M149" s="26" t="s">
-        <v>621</v>
-      </c>
-      <c r="N149" s="52"/>
+        <v>609</v>
+      </c>
+      <c r="N149" s="57"/>
       <c r="O149" s="50"/>
       <c r="P149" s="50" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="Q149" s="50" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="150" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B150" s="52"/>
-      <c r="C150" s="52"/>
-      <c r="D150" s="52"/>
-      <c r="E150" s="52"/>
-      <c r="F150" s="52"/>
-      <c r="G150" s="52"/>
-      <c r="H150" s="52"/>
-      <c r="I150" s="52"/>
-      <c r="J150" s="52"/>
-      <c r="K150" s="52"/>
+      <c r="B150" s="57"/>
+      <c r="C150" s="57"/>
+      <c r="D150" s="57"/>
+      <c r="E150" s="57"/>
+      <c r="F150" s="57"/>
+      <c r="G150" s="57"/>
+      <c r="H150" s="57"/>
+      <c r="I150" s="57"/>
+      <c r="J150" s="57"/>
+      <c r="K150" s="57"/>
       <c r="L150" s="22" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="M150" s="26" t="s">
-        <v>624</v>
-      </c>
-      <c r="N150" s="52"/>
+        <v>612</v>
+      </c>
+      <c r="N150" s="57"/>
       <c r="O150" s="50"/>
       <c r="P150" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q150" s="50"/>
+        <v>39</v>
+      </c>
+      <c r="Q150" s="50" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="151" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B151" s="52"/>
-      <c r="C151" s="52"/>
-      <c r="D151" s="52"/>
-      <c r="E151" s="52"/>
-      <c r="F151" s="52"/>
-      <c r="G151" s="52"/>
-      <c r="H151" s="52"/>
-      <c r="I151" s="52"/>
-      <c r="J151" s="52"/>
-      <c r="K151" s="52"/>
+      <c r="B151" s="57"/>
+      <c r="C151" s="57"/>
+      <c r="D151" s="57"/>
+      <c r="E151" s="57"/>
+      <c r="F151" s="57"/>
+      <c r="G151" s="57"/>
+      <c r="H151" s="57"/>
+      <c r="I151" s="57"/>
+      <c r="J151" s="57"/>
+      <c r="K151" s="57"/>
       <c r="L151" s="22" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="M151" s="26" t="s">
-        <v>626</v>
-      </c>
-      <c r="N151" s="52"/>
+        <v>614</v>
+      </c>
+      <c r="N151" s="57"/>
       <c r="O151" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P151" s="50" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q151" s="50"/>
+        <v>615</v>
+      </c>
+      <c r="Q151" s="50" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="152" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B152" s="52"/>
-      <c r="C152" s="52"/>
-      <c r="D152" s="52"/>
-      <c r="E152" s="52"/>
-      <c r="F152" s="52"/>
-      <c r="G152" s="52"/>
-      <c r="H152" s="52"/>
-      <c r="I152" s="52"/>
-      <c r="J152" s="52"/>
-      <c r="K152" s="52"/>
+      <c r="B152" s="57"/>
+      <c r="C152" s="57"/>
+      <c r="D152" s="57"/>
+      <c r="E152" s="57"/>
+      <c r="F152" s="57"/>
+      <c r="G152" s="57"/>
+      <c r="H152" s="57"/>
+      <c r="I152" s="57"/>
+      <c r="J152" s="57"/>
+      <c r="K152" s="57"/>
       <c r="L152" s="22" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="M152" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="N152" s="52"/>
+        <v>617</v>
+      </c>
+      <c r="N152" s="57"/>
       <c r="O152" s="50"/>
       <c r="P152" s="50" t="s">
-        <v>630</v>
-      </c>
-      <c r="Q152" s="50"/>
+        <v>662</v>
+      </c>
+      <c r="Q152" s="50" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="153" spans="2:17" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B153" s="52"/>
-      <c r="C153" s="52"/>
-      <c r="D153" s="52"/>
-      <c r="E153" s="52"/>
-      <c r="F153" s="52"/>
-      <c r="G153" s="53"/>
-      <c r="H153" s="53"/>
-      <c r="I153" s="52"/>
-      <c r="J153" s="52"/>
-      <c r="K153" s="52"/>
+      <c r="B153" s="57"/>
+      <c r="C153" s="57"/>
+      <c r="D153" s="57"/>
+      <c r="E153" s="57"/>
+      <c r="F153" s="57"/>
+      <c r="G153" s="54"/>
+      <c r="H153" s="54"/>
+      <c r="I153" s="57"/>
+      <c r="J153" s="57"/>
+      <c r="K153" s="57"/>
       <c r="L153" s="22" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="M153" s="26" t="s">
-        <v>632</v>
-      </c>
-      <c r="N153" s="52"/>
+        <v>619</v>
+      </c>
+      <c r="N153" s="57"/>
       <c r="O153" s="50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P153" s="50" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q153" s="50"/>
+        <v>620</v>
+      </c>
+      <c r="Q153" s="50" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="154" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B154" s="68">
+      <c r="B154" s="53">
         <v>7</v>
       </c>
-      <c r="C154" s="68" t="s">
-        <v>634</v>
-      </c>
-      <c r="D154" s="71" t="s">
-        <v>635</v>
-      </c>
-      <c r="E154" s="68" t="s">
-        <v>636</v>
-      </c>
-      <c r="F154" s="71" t="s">
-        <v>637</v>
+      <c r="C154" s="53" t="s">
+        <v>621</v>
+      </c>
+      <c r="D154" s="70" t="s">
+        <v>622</v>
+      </c>
+      <c r="E154" s="53" t="s">
+        <v>623</v>
+      </c>
+      <c r="F154" s="70" t="s">
+        <v>624</v>
       </c>
       <c r="G154" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H154" s="68" t="s">
+      <c r="H154" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="I154" s="51" t="s">
-        <v>638</v>
-      </c>
-      <c r="J154" s="51" t="s">
-        <v>639</v>
+      <c r="I154" s="55" t="s">
+        <v>625</v>
+      </c>
+      <c r="J154" s="55" t="s">
+        <v>626</v>
       </c>
       <c r="K154" s="27" t="s">
         <v>5</v>
       </c>
       <c r="L154" s="22" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="M154" s="26" t="s">
-        <v>641</v>
-      </c>
-      <c r="N154" s="68" t="s">
-        <v>642</v>
+        <v>628</v>
+      </c>
+      <c r="N154" s="53" t="s">
+        <v>629</v>
       </c>
       <c r="O154" s="50"/>
       <c r="P154" s="50" t="s">
-        <v>643</v>
-      </c>
-      <c r="Q154" s="50"/>
+        <v>630</v>
+      </c>
+      <c r="Q154" s="51" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="155" spans="2:17" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B155" s="53"/>
-      <c r="C155" s="53"/>
-      <c r="D155" s="53"/>
-      <c r="E155" s="53"/>
-      <c r="F155" s="53"/>
+      <c r="B155" s="54"/>
+      <c r="C155" s="54"/>
+      <c r="D155" s="54"/>
+      <c r="E155" s="54"/>
+      <c r="F155" s="54"/>
       <c r="G155" s="33"/>
-      <c r="H155" s="53"/>
-      <c r="I155" s="53"/>
-      <c r="J155" s="53"/>
+      <c r="H155" s="54"/>
+      <c r="I155" s="54"/>
+      <c r="J155" s="54"/>
       <c r="K155" s="27" t="s">
         <v>6</v>
       </c>
       <c r="L155" s="22" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="M155" s="26" t="s">
-        <v>645</v>
-      </c>
-      <c r="N155" s="53"/>
+        <v>632</v>
+      </c>
+      <c r="N155" s="54"/>
       <c r="O155" s="22"/>
       <c r="P155" s="50" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q155" s="50"/>
+        <v>633</v>
+      </c>
+      <c r="Q155" s="50" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="157" spans="2:17" x14ac:dyDescent="0.4">
       <c r="K157" s="25"/>
@@ -7826,6 +8585,243 @@
   </sheetData>
   <autoFilter ref="B2:N155" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="261">
+    <mergeCell ref="K138:K139"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="K103:K105"/>
+    <mergeCell ref="F82:F84"/>
+    <mergeCell ref="K143:K145"/>
+    <mergeCell ref="K70:K73"/>
+    <mergeCell ref="K95:K97"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="C140:C147"/>
+    <mergeCell ref="K110:K112"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F62:F69"/>
+    <mergeCell ref="H146:H147"/>
+    <mergeCell ref="K131:K137"/>
+    <mergeCell ref="I36:I39"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="H140:H142"/>
+    <mergeCell ref="K86:K90"/>
+    <mergeCell ref="J143:J145"/>
+    <mergeCell ref="K129:K130"/>
+    <mergeCell ref="J146:J147"/>
+    <mergeCell ref="H77:H81"/>
+    <mergeCell ref="K120:K122"/>
+    <mergeCell ref="D140:D145"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="F131:F139"/>
+    <mergeCell ref="H113:H118"/>
+    <mergeCell ref="K106:K107"/>
+    <mergeCell ref="I146:I147"/>
+    <mergeCell ref="H131:H139"/>
+    <mergeCell ref="J36:J39"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="I53:I57"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="I143:I145"/>
+    <mergeCell ref="I131:I139"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="F146:F147"/>
+    <mergeCell ref="H42:H49"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="J77:J81"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="K91:K94"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F103:F105"/>
+    <mergeCell ref="F85:F90"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="H103:H105"/>
+    <mergeCell ref="N140:N147"/>
+    <mergeCell ref="F29:F35"/>
+    <mergeCell ref="G123:G124"/>
+    <mergeCell ref="H85:H90"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C148:C153"/>
+    <mergeCell ref="J113:J118"/>
+    <mergeCell ref="D22:D28"/>
+    <mergeCell ref="E148:E153"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="F42:F49"/>
+    <mergeCell ref="K126:K128"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="G148:G153"/>
+    <mergeCell ref="B58:B139"/>
+    <mergeCell ref="I148:I153"/>
+    <mergeCell ref="J123:J125"/>
+    <mergeCell ref="K148:K153"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="E131:E139"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="J95:J97"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H98:H102"/>
+    <mergeCell ref="G82:G84"/>
+    <mergeCell ref="K77:K81"/>
+    <mergeCell ref="J98:J102"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="J62:J69"/>
+    <mergeCell ref="J50:J52"/>
+    <mergeCell ref="J70:J74"/>
+    <mergeCell ref="F140:F142"/>
+    <mergeCell ref="G70:G73"/>
+    <mergeCell ref="I95:I97"/>
+    <mergeCell ref="J91:J94"/>
+    <mergeCell ref="G77:G81"/>
+    <mergeCell ref="I70:I74"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="N3:N28"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="I85:I90"/>
+    <mergeCell ref="D106:D112"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="I29:I35"/>
+    <mergeCell ref="F36:F39"/>
+    <mergeCell ref="K53:K57"/>
+    <mergeCell ref="J110:J112"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="N148:N153"/>
+    <mergeCell ref="K50:K52"/>
+    <mergeCell ref="E146:E147"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="D131:D139"/>
+    <mergeCell ref="F95:F97"/>
+    <mergeCell ref="F70:F74"/>
+    <mergeCell ref="K146:K147"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="K140:K142"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="C58:C139"/>
+    <mergeCell ref="I58:I61"/>
+    <mergeCell ref="K58:K61"/>
+    <mergeCell ref="J29:J35"/>
+    <mergeCell ref="B3:B21"/>
+    <mergeCell ref="H126:H130"/>
+    <mergeCell ref="H148:H153"/>
+    <mergeCell ref="F91:F94"/>
+    <mergeCell ref="J126:J130"/>
+    <mergeCell ref="J148:J153"/>
+    <mergeCell ref="H82:H84"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="I120:I122"/>
+    <mergeCell ref="I62:I69"/>
+    <mergeCell ref="F113:F118"/>
+    <mergeCell ref="F53:F57"/>
+    <mergeCell ref="H53:H57"/>
+    <mergeCell ref="D113:D130"/>
+    <mergeCell ref="F143:F145"/>
+    <mergeCell ref="H143:H145"/>
+    <mergeCell ref="K113:K115"/>
+    <mergeCell ref="E6:E15"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="J131:J139"/>
+    <mergeCell ref="H110:H112"/>
+    <mergeCell ref="K123:K124"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="C3:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="F154:F155"/>
+    <mergeCell ref="I91:I94"/>
+    <mergeCell ref="E29:E52"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I123:I125"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="J6:J9"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="I110:I112"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="D6:D15"/>
+    <mergeCell ref="F123:F125"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="I113:I118"/>
+    <mergeCell ref="E113:E130"/>
+    <mergeCell ref="E154:E155"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="J120:J122"/>
+    <mergeCell ref="F98:F102"/>
+    <mergeCell ref="I77:I81"/>
+    <mergeCell ref="E53:E57"/>
+    <mergeCell ref="J82:J84"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="F110:F112"/>
+    <mergeCell ref="J85:J90"/>
+    <mergeCell ref="G62:G69"/>
+    <mergeCell ref="E58:E97"/>
+    <mergeCell ref="J53:J57"/>
+    <mergeCell ref="F77:F81"/>
+    <mergeCell ref="D148:D153"/>
+    <mergeCell ref="F126:F130"/>
+    <mergeCell ref="F148:F153"/>
+    <mergeCell ref="H62:H69"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J58:J61"/>
+    <mergeCell ref="J103:J105"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="D53:D57"/>
+    <mergeCell ref="G58:G61"/>
+    <mergeCell ref="H36:H39"/>
+    <mergeCell ref="D58:D97"/>
+    <mergeCell ref="G140:G142"/>
+    <mergeCell ref="H70:H74"/>
+    <mergeCell ref="I140:I142"/>
+    <mergeCell ref="E106:E112"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="G131:G137"/>
+    <mergeCell ref="J154:J155"/>
+    <mergeCell ref="J140:J142"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="B29:B57"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="I82:I84"/>
+    <mergeCell ref="J42:J49"/>
+    <mergeCell ref="K62:K69"/>
+    <mergeCell ref="K82:K84"/>
+    <mergeCell ref="I154:I155"/>
+    <mergeCell ref="N29:N57"/>
+    <mergeCell ref="K116:K118"/>
+    <mergeCell ref="I98:I102"/>
+    <mergeCell ref="H95:H97"/>
+    <mergeCell ref="H120:H122"/>
+    <mergeCell ref="K98:K102"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="I50:I52"/>
+    <mergeCell ref="B140:B147"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="F120:F122"/>
+    <mergeCell ref="E98:E105"/>
     <mergeCell ref="N154:N155"/>
     <mergeCell ref="I40:I41"/>
     <mergeCell ref="N58:N139"/>
@@ -7850,243 +8846,6 @@
     <mergeCell ref="D29:D52"/>
     <mergeCell ref="D98:D105"/>
     <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B29:B57"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="J42:J49"/>
-    <mergeCell ref="K62:K69"/>
-    <mergeCell ref="K82:K84"/>
-    <mergeCell ref="I154:I155"/>
-    <mergeCell ref="N29:N57"/>
-    <mergeCell ref="K116:K118"/>
-    <mergeCell ref="I98:I102"/>
-    <mergeCell ref="H95:H97"/>
-    <mergeCell ref="H120:H122"/>
-    <mergeCell ref="K98:K102"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="I16:I19"/>
-    <mergeCell ref="I50:I52"/>
-    <mergeCell ref="B140:B147"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="F120:F122"/>
-    <mergeCell ref="E98:E105"/>
-    <mergeCell ref="D148:D153"/>
-    <mergeCell ref="F126:F130"/>
-    <mergeCell ref="F148:F153"/>
-    <mergeCell ref="H62:H69"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="J58:J61"/>
-    <mergeCell ref="J103:J105"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="D53:D57"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="H36:H39"/>
-    <mergeCell ref="D58:D97"/>
-    <mergeCell ref="G140:G142"/>
-    <mergeCell ref="H70:H74"/>
-    <mergeCell ref="I140:I142"/>
-    <mergeCell ref="E106:E112"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="G131:G137"/>
-    <mergeCell ref="J154:J155"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="J77:J81"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="F110:F112"/>
-    <mergeCell ref="J131:J139"/>
-    <mergeCell ref="H110:H112"/>
-    <mergeCell ref="K123:K124"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="I6:I9"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="J120:J122"/>
-    <mergeCell ref="F98:F102"/>
-    <mergeCell ref="I77:I81"/>
-    <mergeCell ref="E53:E57"/>
-    <mergeCell ref="J140:J142"/>
-    <mergeCell ref="J82:J84"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="I95:I97"/>
-    <mergeCell ref="J91:J94"/>
-    <mergeCell ref="G77:G81"/>
-    <mergeCell ref="I70:I74"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="H146:H147"/>
-    <mergeCell ref="K131:K137"/>
-    <mergeCell ref="I36:I39"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="C3:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="K75:K76"/>
-    <mergeCell ref="F154:F155"/>
-    <mergeCell ref="I91:I94"/>
-    <mergeCell ref="E29:E52"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I123:I125"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="J6:J9"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="I110:I112"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="D6:D15"/>
-    <mergeCell ref="F123:F125"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="I113:I118"/>
-    <mergeCell ref="E113:E130"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="H126:H130"/>
-    <mergeCell ref="H148:H153"/>
-    <mergeCell ref="F91:F94"/>
-    <mergeCell ref="J126:J130"/>
-    <mergeCell ref="J148:J153"/>
-    <mergeCell ref="H82:H84"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="I120:I122"/>
-    <mergeCell ref="I62:I69"/>
-    <mergeCell ref="F113:F118"/>
-    <mergeCell ref="F53:F57"/>
-    <mergeCell ref="H53:H57"/>
-    <mergeCell ref="D113:D130"/>
-    <mergeCell ref="F143:F145"/>
-    <mergeCell ref="H143:H145"/>
-    <mergeCell ref="K113:K115"/>
-    <mergeCell ref="E6:E15"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="J85:J90"/>
-    <mergeCell ref="G62:G69"/>
-    <mergeCell ref="E58:E97"/>
-    <mergeCell ref="J53:J57"/>
-    <mergeCell ref="N3:N28"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="I85:I90"/>
-    <mergeCell ref="D106:D112"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="H58:H61"/>
-    <mergeCell ref="I29:I35"/>
-    <mergeCell ref="F36:F39"/>
-    <mergeCell ref="K53:K57"/>
-    <mergeCell ref="J110:J112"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="N148:N153"/>
-    <mergeCell ref="K50:K52"/>
-    <mergeCell ref="E146:E147"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="D131:D139"/>
-    <mergeCell ref="F95:F97"/>
-    <mergeCell ref="F70:F74"/>
-    <mergeCell ref="K146:K147"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="K140:K142"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="E154:E155"/>
-    <mergeCell ref="C58:C139"/>
-    <mergeCell ref="I58:I61"/>
-    <mergeCell ref="K58:K61"/>
-    <mergeCell ref="J29:J35"/>
-    <mergeCell ref="E16:E19"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="K110:K112"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F62:F69"/>
-    <mergeCell ref="I148:I153"/>
-    <mergeCell ref="J123:J125"/>
-    <mergeCell ref="K148:K153"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E131:E139"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="J95:J97"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H98:H102"/>
-    <mergeCell ref="G82:G84"/>
-    <mergeCell ref="K77:K81"/>
-    <mergeCell ref="J98:J102"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="B148:B153"/>
-    <mergeCell ref="K91:K94"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F103:F105"/>
-    <mergeCell ref="F85:F90"/>
-    <mergeCell ref="K33:K35"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="H103:H105"/>
-    <mergeCell ref="N140:N147"/>
-    <mergeCell ref="F29:F35"/>
-    <mergeCell ref="G123:G124"/>
-    <mergeCell ref="H85:H90"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C148:C153"/>
-    <mergeCell ref="J113:J118"/>
-    <mergeCell ref="D22:D28"/>
-    <mergeCell ref="E148:E153"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="F42:F49"/>
-    <mergeCell ref="K126:K128"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G148:G153"/>
-    <mergeCell ref="B58:B139"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="J146:J147"/>
-    <mergeCell ref="H77:H81"/>
-    <mergeCell ref="K120:K122"/>
-    <mergeCell ref="D140:D145"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="F131:F139"/>
-    <mergeCell ref="H113:H118"/>
-    <mergeCell ref="K106:K107"/>
-    <mergeCell ref="I146:I147"/>
-    <mergeCell ref="H131:H139"/>
-    <mergeCell ref="J36:J39"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="I53:I57"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C140:C147"/>
-    <mergeCell ref="I143:I145"/>
-    <mergeCell ref="I131:I139"/>
-    <mergeCell ref="F16:F19"/>
-    <mergeCell ref="F146:F147"/>
-    <mergeCell ref="H42:H49"/>
-    <mergeCell ref="J62:J69"/>
-    <mergeCell ref="J50:J52"/>
-    <mergeCell ref="J70:J74"/>
-    <mergeCell ref="F140:F142"/>
-    <mergeCell ref="G70:G73"/>
-    <mergeCell ref="H140:H142"/>
-    <mergeCell ref="K86:K90"/>
-    <mergeCell ref="J143:J145"/>
-    <mergeCell ref="K129:K130"/>
-    <mergeCell ref="F77:F81"/>
-    <mergeCell ref="K138:K139"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="K103:K105"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="K143:K145"/>
-    <mergeCell ref="K70:K73"/>
-    <mergeCell ref="K95:K97"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
